--- a/recettes.xlsx
+++ b/recettes.xlsx
@@ -47,41 +47,41 @@
   <numFmts count="0"/>
   <fonts count="6">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
       <b val="1"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -475,7 +475,7 @@
       </c>
       <c r="M1" s="6" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
     </row>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Poulet rôti et pommes de terre 🌱 Carottes nouvelles</t>
+          <t>Poulet rôti et pommes de terre 🌷 Carottes nouvelles</t>
         </is>
       </c>
       <c r="C3" s="10" t="n"/>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet rôti, Pommes de terre, Carottes nouvelles). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet rôti, Pommes de terre, Carottes nouvelles).</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Répartir les carottes nouvelles dans le plat. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Répartir les carottes nouvelles dans le plat.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Déposer et assaisonner le poulet. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Déposer et assaisonner le poulet.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Cuire environ une heure à 190 °C. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 70 minutes.</t>
+          <t>Cuire environ une heure à 190 °C.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet rôti, Pommes de terre, Courgettes). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet rôti, Pommes de terre, Courgettes).</t>
         </is>
       </c>
       <c r="C41" s="10" t="n"/>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Répartir la courgettes dans le plat. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Répartir la courgettes dans le plat.</t>
         </is>
       </c>
       <c r="C42" s="10" t="n"/>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Déposer et assaisonner le poulet. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Déposer et assaisonner le poulet.</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Cuire environ une heure à 190 °C. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 70 minutes.</t>
+          <t>Cuire environ une heure à 190 °C.</t>
         </is>
       </c>
       <c r="C44" s="10" t="n"/>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C47" s="9" t="n"/>
@@ -10648,7 +10648,7 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Poulet rôti et pommes de terre 🍁 Courge</t>
+          <t>Poulet rôti et pommes de terre 🍂 Courge</t>
         </is>
       </c>
       <c r="C49" s="10" t="n"/>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet rôti, Pommes de terre, Courge). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet rôti, Pommes de terre, Courge).</t>
         </is>
       </c>
       <c r="C64" s="10" t="n"/>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Répartir la courge dans le plat. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Répartir la courge dans le plat.</t>
         </is>
       </c>
       <c r="C65" s="10" t="n"/>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Déposer et assaisonner le poulet. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Déposer et assaisonner le poulet.</t>
         </is>
       </c>
       <c r="C66" s="10" t="n"/>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Cuire environ une heure à 190 °C. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 70 minutes.</t>
+          <t>Cuire environ une heure à 190 °C.</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -11000,7 +11000,7 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C70" s="9" t="n"/>
@@ -11310,7 +11310,7 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet rôti, Pommes de terre, Carottes). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet rôti, Pommes de terre, Carottes).</t>
         </is>
       </c>
       <c r="C87" s="10" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Répartir les carottes dans le plat. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Répartir les carottes dans le plat.</t>
         </is>
       </c>
       <c r="C88" s="10" t="n"/>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Déposer et assaisonner le poulet. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Déposer et assaisonner le poulet.</t>
         </is>
       </c>
       <c r="C89" s="10" t="n"/>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Cuire environ une heure à 190 °C. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 70 minutes.</t>
+          <t>Cuire environ une heure à 190 °C.</t>
         </is>
       </c>
       <c r="C90" s="10" t="n"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Aubergine, Courgette, Poivron, Tomates). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Aubergine, Courgette, Poivron, Tomates).</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir les légumes séparément. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire revenir les légumes séparément.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Les réunir avec tomates et oignon. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Les réunir avec tomates et oignon.</t>
         </is>
       </c>
       <c r="C23" s="10" t="n"/>
@@ -11831,7 +11831,7 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Servir avec la semoule. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 40 minutes.</t>
+          <t>Servir avec la semoule.</t>
         </is>
       </c>
       <c r="C24" s="10" t="n"/>
@@ -11872,7 +11872,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Potiron, Stracciatella, Pommes de terre). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Potiron, Stracciatella, Pommes de terre).</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Cuire potiron et pommes de terre. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire potiron et pommes de terre.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Mixer finement. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Mixer finement.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -12220,7 +12220,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Ajouter la stracciatella au service. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Ajouter la stracciatella au service.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saucisse de Morteau, Lentilles vertes, Carottes). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saucisse de Morteau, Lentilles vertes, Carottes).</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Cuire lentilles, carottes et oignon. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire lentilles, carottes et oignon.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Ajouter la saucisse. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter la saucisse.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Trancher et servir. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 45 minutes.</t>
+          <t>Trancher et servir.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Lentilles corail, Carottes, Naan fromage). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Lentilles corail, Carottes, Naan fromage).</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir les carottes avec les épices. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire revenir les carottes avec les épices.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Ajouter les lentilles, le lait de coco et un peu d’eau. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter les lentilles, le lait de coco et un peu d’eau.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Servir avec le naan fromage réchauffé. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Servir avec le naan fromage réchauffé.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -13345,7 +13345,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Lentilles vertes, Pommes de terre, Carottes). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Lentilles vertes, Pommes de terre, Carottes).</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -13359,7 +13359,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Cuire les lentilles avec les légumes. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire les lentilles avec les légumes.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -13373,7 +13373,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Préparer la purée. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Préparer la purée.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Gratiner 20 minutes. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 50 minutes.</t>
+          <t>Gratiner 20 minutes.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -13428,7 +13428,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poireaux, Comté, Pâte brisée, Salade verte). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poireaux, Comté, Pâte brisée, Salade verte).</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Faire fondre les poireaux. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire fondre les poireaux.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -13792,7 +13792,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Garnir la pâte. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Garnir la pâte.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -13806,7 +13806,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Cuire et servir avec la salade. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 50 minutes.</t>
+          <t>Cuire et servir avec la salade.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Salade romaine, Bacon, Parmesan, Pain). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Salade romaine, Bacon, Parmesan, Pain).</t>
         </is>
       </c>
       <c r="C23" s="10" t="n"/>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Griller le bacon et le pain. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Griller le bacon et le pain.</t>
         </is>
       </c>
       <c r="C24" s="10" t="n"/>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Cuire les œufs. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Cuire les œufs.</t>
         </is>
       </c>
       <c r="C25" s="10" t="n"/>
@@ -14345,7 +14345,7 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Assembler tous les ingrédients. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 20 minutes.</t>
+          <t>Assembler tous les ingrédients.</t>
         </is>
       </c>
       <c r="C26" s="10" t="n"/>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -14812,7 +14812,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Sardines, Avocat, Épices guacamole, Salade verte). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Sardines, Avocat, Épices guacamole, Salade verte).</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -14826,7 +14826,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Émincer les échalotes. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Émincer les échalotes.</t>
         </is>
       </c>
       <c r="C23" s="10" t="n"/>
@@ -14840,7 +14840,7 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Assaisonner l’avocat. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Assaisonner l’avocat.</t>
         </is>
       </c>
       <c r="C24" s="10" t="n"/>
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Ajouter sardines et pain complet. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 15 minutes.</t>
+          <t>Ajouter sardines et pain complet.</t>
         </is>
       </c>
       <c r="C25" s="10" t="n"/>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -15201,7 +15201,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Pain, Chèvre, Salade verte). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Pain, Chèvre, Salade verte).</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -15215,7 +15215,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Garnir le pain de chèvre. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Garnir le pain de chèvre.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Faire gratiner. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Faire gratiner.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -15243,7 +15243,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Servir ensemble. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 20 minutes.</t>
+          <t>Servir ensemble.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Poulet moutarde et riz 🌱 Petits pois</t>
+          <t>Poulet moutarde et riz 🌷 Petits pois</t>
         </is>
       </c>
       <c r="C3" s="10" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet, Riz, Crème, Moutarde). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet, Riz, Crème, Moutarde).</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Colorer le poulet. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Colorer le poulet.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -15682,7 +15682,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Ajouter haricots verts et petits pois. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter haricots verts et petits pois.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Mijoter puis servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 40 minutes.</t>
+          <t>Mijoter puis servir avec le riz.</t>
         </is>
       </c>
       <c r="C23" s="10" t="n"/>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C26" s="9" t="n"/>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet, Riz, Crème, Moutarde). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet, Riz, Crème, Moutarde).</t>
         </is>
       </c>
       <c r="C45" s="10" t="n"/>
@@ -16112,7 +16112,7 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Colorer le poulet. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Colorer le poulet.</t>
         </is>
       </c>
       <c r="C46" s="10" t="n"/>
@@ -16126,7 +16126,7 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Ajouter haricots verts. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter haricots verts.</t>
         </is>
       </c>
       <c r="C47" s="10" t="n"/>
@@ -16140,7 +16140,7 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Mijoter puis servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 40 minutes.</t>
+          <t>Mijoter puis servir avec le riz.</t>
         </is>
       </c>
       <c r="C48" s="10" t="n"/>
@@ -16172,7 +16172,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C51" s="9" t="n"/>
@@ -16204,7 +16204,7 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Poulet moutarde et riz 🍁 Courge</t>
+          <t>Poulet moutarde et riz 🍂 Courge</t>
         </is>
       </c>
       <c r="C53" s="10" t="n"/>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet, Riz, Crème, Moutarde). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet, Riz, Crème, Moutarde).</t>
         </is>
       </c>
       <c r="C70" s="10" t="n"/>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Colorer le poulet. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Colorer le poulet.</t>
         </is>
       </c>
       <c r="C71" s="10" t="n"/>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Ajouter haricots verts et courge. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter haricots verts et courge.</t>
         </is>
       </c>
       <c r="C72" s="10" t="n"/>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Mijoter puis servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 40 minutes.</t>
+          <t>Mijoter puis servir avec le riz.</t>
         </is>
       </c>
       <c r="C73" s="10" t="n"/>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C76" s="9" t="n"/>
@@ -16986,7 +16986,7 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet, Riz, Crème, Moutarde). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet, Riz, Crème, Moutarde).</t>
         </is>
       </c>
       <c r="C95" s="10" t="n"/>
@@ -17000,7 +17000,7 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Colorer le poulet. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Colorer le poulet.</t>
         </is>
       </c>
       <c r="C96" s="10" t="n"/>
@@ -17014,7 +17014,7 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Ajouter haricots verts et poireaux. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter haricots verts et poireaux.</t>
         </is>
       </c>
       <c r="C97" s="10" t="n"/>
@@ -17028,7 +17028,7 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Mijoter puis servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 40 minutes.</t>
+          <t>Mijoter puis servir avec le riz.</t>
         </is>
       </c>
       <c r="C98" s="10" t="n"/>
@@ -17069,7 +17069,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -17375,7 +17375,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Haricots rouges, Riz, Tomates concassées). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Haricots rouges, Riz, Tomates concassées).</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -17389,7 +17389,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir oignon et poivron. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire revenir oignon et poivron.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Ajouter tomates, haricots et maïs. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter tomates, haricots et maïs.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 40 minutes.</t>
+          <t>Servir avec le riz.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Pâtes, Lardons, Œufs, Parmesan). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Pâtes, Lardons, Œufs, Parmesan).</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -17808,7 +17808,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Dorer les lardons. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Dorer les lardons.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Mélanger œufs et parmesan. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Mélanger œufs et parmesan.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -17836,7 +17836,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Incorporer la sauce hors du feu. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 25 minutes.</t>
+          <t>Incorporer la sauce hors du feu.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -17877,7 +17877,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -18393,7 +18393,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Pâtes, Bœuf haché, Carottes, Épinards). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Pâtes, Bœuf haché, Carottes, Épinards).</t>
         </is>
       </c>
       <c r="C25" s="10" t="n"/>
@@ -18407,7 +18407,7 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir les légumes. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire revenir les légumes.</t>
         </is>
       </c>
       <c r="C26" s="10" t="n"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Ajouter le bœuf. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter le bœuf.</t>
         </is>
       </c>
       <c r="C27" s="10" t="n"/>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Servir avec les pâtes. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 40 minutes.</t>
+          <t>Servir avec les pâtes.</t>
         </is>
       </c>
       <c r="C28" s="10" t="n"/>
@@ -18476,7 +18476,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Steak haché, Pain burger, Pommes de terre, Salade verte). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Steak haché, Pain burger, Pommes de terre, Salade verte).</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -18826,7 +18826,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Cuire les pommes de terre au four. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire les pommes de terre au four.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -18840,7 +18840,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Cuire les steaks. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Cuire les steaks.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Monter les burgers et servir. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 40 minutes.</t>
+          <t>Monter les burgers et servir.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -18895,7 +18895,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Pain de mie, Jambon, Fromage, Salade verte). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Pain de mie, Jambon, Fromage, Salade verte).</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Garnir les tranches. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Garnir les tranches.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Fermer les croques. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Fermer les croques.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Servir avec la salade. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 20 minutes.</t>
+          <t>Servir avec la salade.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -19314,7 +19314,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -19680,7 +19680,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Œufs, Lait, Jambon, Fromage). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Œufs, Lait, Jambon, Fromage).</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -19694,7 +19694,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Réchauffer la galette. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Réchauffer la galette.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Ajouter jambon, fromage et œuf. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter jambon, fromage et œuf.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Servir avec la salade. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Servir avec la salade.</t>
         </is>
       </c>
       <c r="C23" s="10" t="n"/>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -20099,7 +20099,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Thon, Pâte brisée, Œufs, Salade verte). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Thon, Pâte brisée, Œufs, Salade verte).</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -20113,7 +20113,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Garnir la pâte de moutarde et thon. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Garnir la pâte de moutarde et thon.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -20127,7 +20127,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Verser l’appareil œufs-crème. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Verser l’appareil œufs-crème.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -20141,7 +20141,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Cuire et servir avec la salade. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 45 minutes.</t>
+          <t>Cuire et servir avec la salade.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -20182,7 +20182,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Escalope de poulet, Œufs, Chapelure, Parmesan). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Escalope de poulet, Œufs, Chapelure, Parmesan).</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -20622,7 +20622,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Aplatir les escalopes. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Aplatir les escalopes.</t>
         </is>
       </c>
       <c r="C23" s="10" t="n"/>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Paner avec farine, œuf et chapelure-parmesan. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Paner avec farine, œuf et chapelure-parmesan.</t>
         </is>
       </c>
       <c r="C24" s="10" t="n"/>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Servir avec citron et salade. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 30 minutes.</t>
+          <t>Servir avec citron et salade.</t>
         </is>
       </c>
       <c r="C25" s="10" t="n"/>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Gnocchi, Gorgonzola, Noix). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Gnocchi, Gorgonzola, Noix).</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Faire fondre le gorgonzola dans la crème. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire fondre le gorgonzola dans la crème.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -21025,7 +21025,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Dorer les gnocchi. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Dorer les gnocchi.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -21039,7 +21039,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Servir avec la salade. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 25 minutes.</t>
+          <t>Servir avec la salade.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -21416,7 +21416,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Lasagnes, Épinards, Fromage, Salade verte). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Lasagnes, Épinards, Fromage, Salade verte).</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Préparer la garniture aux épinards. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Préparer la garniture aux épinards.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -21444,7 +21444,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Alterner lasagnes et garniture. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Alterner lasagnes et garniture.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -21458,7 +21458,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Cuire 40 minutes à 180 °C et servir avec la salade. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 55 minutes.</t>
+          <t>Cuire 40 minutes à 180 °C et servir avec la salade.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -21499,7 +21499,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Curry végétarien et riz 🌱 Poivrons</t>
+          <t>Curry végétarien et riz 🌷 Poivrons</t>
         </is>
       </c>
       <c r="C3" s="10" t="n"/>
@@ -21839,7 +21839,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz, Pois chiches, Lait de coco, Poivrons). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz, Pois chiches, Lait de coco, Poivrons).</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -21853,7 +21853,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire revenir l’oignon.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -21867,7 +21867,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Ajouter poivrons. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter poivrons.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Mijoter 20 minutes et servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Mijoter 20 minutes et servir avec le riz.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -21913,7 +21913,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz, Pois chiches, Lait de coco, Courgettes). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz, Pois chiches, Lait de coco, Courgettes).</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -22267,7 +22267,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire revenir l’oignon.</t>
         </is>
       </c>
       <c r="C44" s="10" t="n"/>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Ajouter courgettes. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter courgettes.</t>
         </is>
       </c>
       <c r="C45" s="10" t="n"/>
@@ -22295,7 +22295,7 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Mijoter 20 minutes et servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Mijoter 20 minutes et servir avec le riz.</t>
         </is>
       </c>
       <c r="C46" s="10" t="n"/>
@@ -22327,7 +22327,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C49" s="9" t="n"/>
@@ -22359,7 +22359,7 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Curry végétarien et riz 🍁 Courge</t>
+          <t>Curry végétarien et riz 🍂 Courge</t>
         </is>
       </c>
       <c r="C51" s="10" t="n"/>
@@ -22667,7 +22667,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz, Pois chiches, Lait de coco, Courge). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz, Pois chiches, Lait de coco, Courge).</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -22681,7 +22681,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire revenir l’oignon.</t>
         </is>
       </c>
       <c r="C68" s="10" t="n"/>
@@ -22695,7 +22695,7 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Ajouter courge. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter courge.</t>
         </is>
       </c>
       <c r="C69" s="10" t="n"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Mijoter 20 minutes et servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Mijoter 20 minutes et servir avec le riz.</t>
         </is>
       </c>
       <c r="C70" s="10" t="n"/>
@@ -22741,7 +22741,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C73" s="9" t="n"/>
@@ -23141,7 +23141,7 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz, Lait de coco, Asperges, Poivron). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz, Lait de coco, Asperges, Poivron).</t>
         </is>
       </c>
       <c r="C93" s="10" t="n"/>
@@ -23155,7 +23155,7 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire revenir l’oignon.</t>
         </is>
       </c>
       <c r="C94" s="10" t="n"/>
@@ -23169,7 +23169,7 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Ajouter pois chiches. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Ajouter pois chiches.</t>
         </is>
       </c>
       <c r="C95" s="10" t="n"/>
@@ -23183,7 +23183,7 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Mijoter 20 minutes et servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Mijoter 20 minutes et servir avec le riz.</t>
         </is>
       </c>
       <c r="C96" s="10" t="n"/>
@@ -23224,7 +23224,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Risotto au parmesan 🌱 Petits pois</t>
+          <t>Risotto au parmesan 🌷 Petits pois</t>
         </is>
       </c>
       <c r="C3" s="10" t="n"/>
@@ -23564,7 +23564,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz à risotto, Parmesan, Tomates, Petits pois). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz à risotto, Parmesan, Tomates, Petits pois).</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -23578,7 +23578,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir les petits pois. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire revenir les petits pois.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -23592,7 +23592,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Nacrer le riz. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Nacrer le riz.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Incorporer parmesan et petits pois. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Incorporer parmesan et petits pois.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -23638,7 +23638,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -23978,7 +23978,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz à risotto, Parmesan, Tomates, Courgettes). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz à risotto, Parmesan, Tomates, Courgettes).</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -23992,7 +23992,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir la courgettes. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire revenir la courgettes.</t>
         </is>
       </c>
       <c r="C44" s="10" t="n"/>
@@ -24006,7 +24006,7 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Nacrer le riz. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Nacrer le riz.</t>
         </is>
       </c>
       <c r="C45" s="10" t="n"/>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Incorporer parmesan et courgettes. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Incorporer parmesan et courgettes.</t>
         </is>
       </c>
       <c r="C46" s="10" t="n"/>
@@ -24052,7 +24052,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C49" s="9" t="n"/>
@@ -24084,7 +24084,7 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Risotto au parmesan 🍁 Courge</t>
+          <t>Risotto au parmesan 🍂 Courge</t>
         </is>
       </c>
       <c r="C51" s="10" t="n"/>
@@ -24392,7 +24392,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz à risotto, Parmesan, Tomates, Courge). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz à risotto, Parmesan, Tomates, Courge).</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -24406,7 +24406,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir la courge. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire revenir la courge.</t>
         </is>
       </c>
       <c r="C68" s="10" t="n"/>
@@ -24420,7 +24420,7 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Nacrer le riz. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Nacrer le riz.</t>
         </is>
       </c>
       <c r="C69" s="10" t="n"/>
@@ -24434,7 +24434,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Incorporer parmesan et courge. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Incorporer parmesan et courge.</t>
         </is>
       </c>
       <c r="C70" s="10" t="n"/>
@@ -24466,7 +24466,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C73" s="9" t="n"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz à risotto, Parmesan, Tomates, Poireaux). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz à risotto, Parmesan, Tomates, Poireaux).</t>
         </is>
       </c>
       <c r="C91" s="10" t="n"/>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir les poireaux. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire revenir les poireaux.</t>
         </is>
       </c>
       <c r="C92" s="10" t="n"/>
@@ -24834,7 +24834,7 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Nacrer le riz. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Nacrer le riz.</t>
         </is>
       </c>
       <c r="C93" s="10" t="n"/>
@@ -24848,7 +24848,7 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Incorporer parmesan et poireaux. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Incorporer parmesan et poireaux.</t>
         </is>
       </c>
       <c r="C94" s="10" t="n"/>
@@ -24889,7 +24889,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -24921,7 +24921,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa 🌱 Épinards</t>
+          <t>Galettes de légumes et quinoa 🌷 Épinards</t>
         </is>
       </c>
       <c r="C3" s="10" t="n"/>
@@ -25229,7 +25229,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Quinoa, Œufs, Chapelure, Épinards). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Quinoa, Œufs, Chapelure, Épinards).</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -25243,7 +25243,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Cuire le quinoa. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire le quinoa.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Râper et essorer les épinards. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Râper et essorer les épinards.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -25271,7 +25271,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Former puis dorer les galettes. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 40 minutes.</t>
+          <t>Former puis dorer les galettes.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -25303,7 +25303,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -25643,7 +25643,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Quinoa, Œufs, Chapelure, Courgettes). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Quinoa, Œufs, Chapelure, Courgettes).</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -25657,7 +25657,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Cuire le quinoa. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire le quinoa.</t>
         </is>
       </c>
       <c r="C44" s="10" t="n"/>
@@ -25671,7 +25671,7 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Râper et essorer la courgettes. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Râper et essorer la courgettes.</t>
         </is>
       </c>
       <c r="C45" s="10" t="n"/>
@@ -25685,7 +25685,7 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Former puis dorer les galettes. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 40 minutes.</t>
+          <t>Former puis dorer les galettes.</t>
         </is>
       </c>
       <c r="C46" s="10" t="n"/>
@@ -25717,7 +25717,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C49" s="9" t="n"/>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa 🍁 Courge</t>
+          <t>Galettes de légumes et quinoa 🍂 Courge</t>
         </is>
       </c>
       <c r="C51" s="10" t="n"/>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Quinoa, Œufs, Chapelure, Courge). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Quinoa, Œufs, Chapelure, Courge).</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -26071,7 +26071,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Cuire le quinoa. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire le quinoa.</t>
         </is>
       </c>
       <c r="C68" s="10" t="n"/>
@@ -26085,7 +26085,7 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Râper et essorer la courge. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Râper et essorer la courge.</t>
         </is>
       </c>
       <c r="C69" s="10" t="n"/>
@@ -26099,7 +26099,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Former puis dorer les galettes. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 40 minutes.</t>
+          <t>Former puis dorer les galettes.</t>
         </is>
       </c>
       <c r="C70" s="10" t="n"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C73" s="9" t="n"/>
@@ -26471,7 +26471,7 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Quinoa, Œufs, Chapelure, Poireaux). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Quinoa, Œufs, Chapelure, Poireaux).</t>
         </is>
       </c>
       <c r="C91" s="10" t="n"/>
@@ -26485,7 +26485,7 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Cuire le quinoa. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire le quinoa.</t>
         </is>
       </c>
       <c r="C92" s="10" t="n"/>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Râper et essorer les poireaux. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Râper et essorer les poireaux.</t>
         </is>
       </c>
       <c r="C93" s="10" t="n"/>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Former puis dorer les galettes. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 40 minutes.</t>
+          <t>Former puis dorer les galettes.</t>
         </is>
       </c>
       <c r="C94" s="10" t="n"/>
@@ -26554,7 +26554,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Cabillaud et riz 🌱 Épinards</t>
+          <t>Cabillaud et riz 🌷 Épinards</t>
         </is>
       </c>
       <c r="C3" s="10" t="n"/>
@@ -26894,7 +26894,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Cabillaud, Riz, Tomates, Épinards). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Cabillaud, Riz, Tomates, Épinards).</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -26908,7 +26908,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Faire fondre les épinards. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire fondre les épinards.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Déposer le cabillaud. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Déposer le cabillaud.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -26936,7 +26936,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Servir avec le riz.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -26968,7 +26968,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -27308,7 +27308,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Cabillaud, Riz, Tomates, Courgettes). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Cabillaud, Riz, Tomates, Courgettes).</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -27322,7 +27322,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Faire fondre la courgettes. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire fondre la courgettes.</t>
         </is>
       </c>
       <c r="C44" s="10" t="n"/>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Déposer le cabillaud. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Déposer le cabillaud.</t>
         </is>
       </c>
       <c r="C45" s="10" t="n"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Servir avec le riz.</t>
         </is>
       </c>
       <c r="C46" s="10" t="n"/>
@@ -27382,7 +27382,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C49" s="9" t="n"/>
@@ -27414,7 +27414,7 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Cabillaud et riz 🍁 Courge</t>
+          <t>Cabillaud et riz 🍂 Courge</t>
         </is>
       </c>
       <c r="C51" s="10" t="n"/>
@@ -27722,7 +27722,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Cabillaud, Riz, Tomates, Courge). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Cabillaud, Riz, Tomates, Courge).</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -27736,7 +27736,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Faire fondre la courge. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire fondre la courge.</t>
         </is>
       </c>
       <c r="C68" s="10" t="n"/>
@@ -27750,7 +27750,7 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Déposer le cabillaud. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Déposer le cabillaud.</t>
         </is>
       </c>
       <c r="C69" s="10" t="n"/>
@@ -27764,7 +27764,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Servir avec le riz.</t>
         </is>
       </c>
       <c r="C70" s="10" t="n"/>
@@ -27796,7 +27796,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C73" s="9" t="n"/>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Cabillaud, Riz, Tomates, Poireaux). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Cabillaud, Riz, Tomates, Poireaux).</t>
         </is>
       </c>
       <c r="C91" s="10" t="n"/>
@@ -28150,7 +28150,7 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Faire fondre les poireaux. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Faire fondre les poireaux.</t>
         </is>
       </c>
       <c r="C92" s="10" t="n"/>
@@ -28164,7 +28164,7 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Déposer le cabillaud. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Déposer le cabillaud.</t>
         </is>
       </c>
       <c r="C93" s="10" t="n"/>
@@ -28178,7 +28178,7 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Servir avec le riz. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Servir avec le riz.</t>
         </is>
       </c>
       <c r="C94" s="10" t="n"/>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -28251,7 +28251,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Saumon et quinoa 🌱 Petits pois</t>
+          <t>Saumon et quinoa 🌷 Petits pois</t>
         </is>
       </c>
       <c r="C3" s="10" t="n"/>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saumon, Quinoa, Petits pois). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saumon, Quinoa, Petits pois).</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -28543,7 +28543,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Cuire le quinoa. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire le quinoa.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -28557,7 +28557,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir les petits pois. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Faire revenir les petits pois.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -28571,7 +28571,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Servir ensemble. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Servir ensemble.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -28603,7 +28603,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
@@ -28913,7 +28913,7 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saumon, Quinoa, Courgettes). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saumon, Quinoa, Courgettes).</t>
         </is>
       </c>
       <c r="C41" s="10" t="n"/>
@@ -28927,7 +28927,7 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Cuire le quinoa. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire le quinoa.</t>
         </is>
       </c>
       <c r="C42" s="10" t="n"/>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir la courgettes. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Faire revenir la courgettes.</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -28955,7 +28955,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Servir ensemble. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Servir ensemble.</t>
         </is>
       </c>
       <c r="C44" s="10" t="n"/>
@@ -28987,7 +28987,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C47" s="9" t="n"/>
@@ -29019,7 +29019,7 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Saumon et quinoa 🍁 Courge</t>
+          <t>Saumon et quinoa 🍂 Courge</t>
         </is>
       </c>
       <c r="C49" s="10" t="n"/>
@@ -29297,7 +29297,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saumon, Quinoa, Courge). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saumon, Quinoa, Courge).</t>
         </is>
       </c>
       <c r="C64" s="10" t="n"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Cuire le quinoa. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire le quinoa.</t>
         </is>
       </c>
       <c r="C65" s="10" t="n"/>
@@ -29325,7 +29325,7 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir la courge. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Faire revenir la courge.</t>
         </is>
       </c>
       <c r="C66" s="10" t="n"/>
@@ -29339,7 +29339,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Servir ensemble. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Servir ensemble.</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -29371,7 +29371,7 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C70" s="9" t="n"/>
@@ -29681,7 +29681,7 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saumon, Quinoa, Poireaux). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saumon, Quinoa, Poireaux).</t>
         </is>
       </c>
       <c r="C87" s="10" t="n"/>
@@ -29695,7 +29695,7 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Cuire le quinoa. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire le quinoa.</t>
         </is>
       </c>
       <c r="C88" s="10" t="n"/>
@@ -29709,7 +29709,7 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Faire revenir les poireaux. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Faire revenir les poireaux.</t>
         </is>
       </c>
       <c r="C89" s="10" t="n"/>
@@ -29723,7 +29723,7 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Servir ensemble. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 35 minutes.</t>
+          <t>Servir ensemble.</t>
         </is>
       </c>
       <c r="C90" s="10" t="n"/>
@@ -29764,7 +29764,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -29796,7 +29796,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Quiche au fromage 🌱 Épinards</t>
+          <t>Quiche au fromage 🌷 Épinards</t>
         </is>
       </c>
       <c r="C3" s="10" t="n"/>
@@ -30104,7 +30104,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pâte brisée, Œufs, Épinards). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pâte brisée, Œufs, Épinards).</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -30118,7 +30118,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Préparer les épinards. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Préparer les épinards.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -30132,7 +30132,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Garnir la pâte. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Garnir la pâte.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Cuire et servir avec la salade. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 45 minutes.</t>
+          <t>Cuire et servir avec la salade.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -30178,7 +30178,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pâte brisée, Œufs, Courgettes). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pâte brisée, Œufs, Courgettes).</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -30532,7 +30532,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Préparer les épinards. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Préparer les épinards.</t>
         </is>
       </c>
       <c r="C44" s="10" t="n"/>
@@ -30546,7 +30546,7 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Garnir la pâte. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Garnir la pâte.</t>
         </is>
       </c>
       <c r="C45" s="10" t="n"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Cuire et servir avec la salade. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 45 minutes.</t>
+          <t>Cuire et servir avec la salade.</t>
         </is>
       </c>
       <c r="C46" s="10" t="n"/>
@@ -30592,7 +30592,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C49" s="9" t="n"/>
@@ -30624,7 +30624,7 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Quiche au fromage 🍁 Courge</t>
+          <t>Quiche au fromage 🍂 Courge</t>
         </is>
       </c>
       <c r="C51" s="10" t="n"/>
@@ -30932,7 +30932,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pâte brisée, Œufs, Courge). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pâte brisée, Œufs, Courge).</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -30946,7 +30946,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Préparer les épinards. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Préparer les épinards.</t>
         </is>
       </c>
       <c r="C68" s="10" t="n"/>
@@ -30960,7 +30960,7 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Garnir la pâte. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Garnir la pâte.</t>
         </is>
       </c>
       <c r="C69" s="10" t="n"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Cuire et servir avec la salade. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 45 minutes.</t>
+          <t>Cuire et servir avec la salade.</t>
         </is>
       </c>
       <c r="C70" s="10" t="n"/>
@@ -31006,7 +31006,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C73" s="9" t="n"/>
@@ -31346,7 +31346,7 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pâte brisée, Œufs, Poireaux). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pâte brisée, Œufs, Poireaux).</t>
         </is>
       </c>
       <c r="C91" s="10" t="n"/>
@@ -31360,7 +31360,7 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Préparer les épinards. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Préparer les épinards.</t>
         </is>
       </c>
       <c r="C92" s="10" t="n"/>
@@ -31374,7 +31374,7 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Garnir la pâte. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Garnir la pâte.</t>
         </is>
       </c>
       <c r="C93" s="10" t="n"/>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Cuire et servir avec la salade. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 45 minutes.</t>
+          <t>Cuire et servir avec la salade.</t>
         </is>
       </c>
       <c r="C94" s="10" t="n"/>
@@ -31429,7 +31429,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -31461,7 +31461,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Gratin au fromage 🌱 Épinards</t>
+          <t>Gratin au fromage 🌷 Épinards</t>
         </is>
       </c>
       <c r="C3" s="10" t="n"/>
@@ -31739,7 +31739,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pommes de terre, Épinards). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pommes de terre, Épinards).</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -31753,7 +31753,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Cuire poireaux et pommes de terre. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire poireaux et pommes de terre.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -31767,7 +31767,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Disposer dans un plat. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Disposer dans un plat.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -31781,7 +31781,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Gratiner au four. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 45 minutes.</t>
+          <t>Gratiner au four.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
@@ -32123,7 +32123,7 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pommes de terre, Courgettes). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pommes de terre, Courgettes).</t>
         </is>
       </c>
       <c r="C41" s="10" t="n"/>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Cuire poireaux et pommes de terre. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire poireaux et pommes de terre.</t>
         </is>
       </c>
       <c r="C42" s="10" t="n"/>
@@ -32151,7 +32151,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Disposer dans un plat. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Disposer dans un plat.</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -32165,7 +32165,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Gratiner au four. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 45 minutes.</t>
+          <t>Gratiner au four.</t>
         </is>
       </c>
       <c r="C44" s="10" t="n"/>
@@ -32197,7 +32197,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C47" s="9" t="n"/>
@@ -32229,7 +32229,7 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Gratin au fromage 🍁 Courge</t>
+          <t>Gratin au fromage 🍂 Courge</t>
         </is>
       </c>
       <c r="C49" s="10" t="n"/>
@@ -32507,7 +32507,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pommes de terre, Courge). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pommes de terre, Courge).</t>
         </is>
       </c>
       <c r="C64" s="10" t="n"/>
@@ -32521,7 +32521,7 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Cuire poireaux et pommes de terre. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire poireaux et pommes de terre.</t>
         </is>
       </c>
       <c r="C65" s="10" t="n"/>
@@ -32535,7 +32535,7 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Disposer dans un plat. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Disposer dans un plat.</t>
         </is>
       </c>
       <c r="C66" s="10" t="n"/>
@@ -32549,7 +32549,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Gratiner au four. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 45 minutes.</t>
+          <t>Gratiner au four.</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -32581,7 +32581,7 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>4.4.0</t>
+          <t>4.5.0</t>
         </is>
       </c>
       <c r="C70" s="9" t="n"/>
@@ -32891,7 +32891,7 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pommes de terre, Poireaux). Laver ou égoutter les produits concernés, puis les découper de façon régulière pour assurer une cuisson homogène.</t>
+          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pommes de terre, Poireaux).</t>
         </is>
       </c>
       <c r="C87" s="10" t="n"/>
@@ -32905,7 +32905,7 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Cuire poireaux et pommes de terre. Utiliser une poêle ou une casserole adaptée, ajouter un filet d’huile si nécessaire et cuire à feu moyen en remuant régulièrement, sans laisser colorer excessivement.</t>
+          <t>Cuire poireaux et pommes de terre.</t>
         </is>
       </c>
       <c r="C88" s="10" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Disposer dans un plat. Ajouter ensuite les autres ingrédients dans l’ordre de la recette. Assaisonner progressivement, mélanger soigneusement et surveiller la texture jusqu’à cuisson complète.</t>
+          <t>Disposer dans un plat.</t>
         </is>
       </c>
       <c r="C89" s="10" t="n"/>
@@ -32933,7 +32933,7 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Gratiner au four. Vérifier la cuisson, rectifier le sel, le poivre et les épices, puis laisser reposer 2 minutes avant de dresser et servir chaud. Temps total indicatif : 45 minutes.</t>
+          <t>Gratiner au four.</t>
         </is>
       </c>
       <c r="C90" s="10" t="n"/>

--- a/recettes.xlsx
+++ b/recettes.xlsx
@@ -36,6 +36,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escalope milanaise et salade ve" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gnocchi au gorgonzola et noix" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lasagne épinards et salade vert" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desserts" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -45,46 +46,50 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
+      <family val="0"/>
       <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +114,11 @@
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0023855B"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -129,7 +139,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -163,6 +173,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -475,7 +491,7 @@
       </c>
       <c r="M1" s="6" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
     </row>
@@ -9848,7 +9864,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -10158,7 +10174,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet rôti, Pommes de terre, Carottes nouvelles).</t>
+          <t>Préchauffer le four à 190 °C et couper les légumes.</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -10232,7 +10248,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
@@ -10542,7 +10558,7 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet rôti, Pommes de terre, Courgettes).</t>
+          <t>Préchauffer le four à 190 °C et couper les légumes.</t>
         </is>
       </c>
       <c r="C41" s="10" t="n"/>
@@ -10616,7 +10632,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C47" s="9" t="n"/>
@@ -10926,7 +10942,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet rôti, Pommes de terre, Courge).</t>
+          <t>Préchauffer le four à 190 °C et couper les légumes.</t>
         </is>
       </c>
       <c r="C64" s="10" t="n"/>
@@ -11000,7 +11016,7 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C70" s="9" t="n"/>
@@ -11310,7 +11326,7 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet rôti, Pommes de terre, Carottes).</t>
+          <t>Préchauffer le four à 190 °C et couper les légumes.</t>
         </is>
       </c>
       <c r="C87" s="10" t="n"/>
@@ -11393,7 +11409,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -11789,7 +11805,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Aubergine, Courgette, Poivron, Tomates).</t>
+          <t>Laver puis couper les légumes en morceaux.</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -11872,7 +11888,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -12178,7 +12194,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Potiron, Stracciatella, Pommes de terre).</t>
+          <t>Éplucher et couper le potiron et les pommes de terre.</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -12261,7 +12277,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -12567,7 +12583,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saucisse de Morteau, Lentilles vertes, Carottes).</t>
+          <t>Rincer les lentilles et couper les carottes.</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -12650,7 +12666,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -12956,7 +12972,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Lentilles corail, Carottes, Naan fromage).</t>
+          <t>Rincer les lentilles et couper les carottes.</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -13039,7 +13055,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -13345,7 +13361,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Lentilles vertes, Pommes de terre, Carottes).</t>
+          <t>Éplucher les pommes de terre et couper les carottes.</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -13428,7 +13444,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -13764,7 +13780,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poireaux, Comté, Pâte brisée, Salade verte).</t>
+          <t>Préchauffer le four à 180 °C et émincer les poireaux.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -13847,7 +13863,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -14303,7 +14319,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Salade romaine, Bacon, Parmesan, Pain).</t>
+          <t>Laver la salade et préparer les ingrédients.</t>
         </is>
       </c>
       <c r="C23" s="10" t="n"/>
@@ -14386,7 +14402,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -14812,7 +14828,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Sardines, Avocat, Épices guacamole, Salade verte).</t>
+          <t>Égoutter les sardines et laver la salade.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -14895,7 +14911,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -15201,7 +15217,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Pain, Chèvre, Salade verte).</t>
+          <t>Préchauffer le four et préparer les tranches de pain.</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -15284,7 +15300,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -15654,7 +15670,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet, Riz, Crème, Moutarde).</t>
+          <t>Cuire le riz selon les indications du paquet.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -15682,7 +15698,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Ajouter haricots verts et petits pois.</t>
+          <t>Ajouter les petits pois.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -15728,7 +15744,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C26" s="9" t="n"/>
@@ -16098,7 +16114,7 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet, Riz, Crème, Moutarde).</t>
+          <t>Cuire le riz selon les indications du paquet.</t>
         </is>
       </c>
       <c r="C45" s="10" t="n"/>
@@ -16172,7 +16188,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C51" s="9" t="n"/>
@@ -16542,7 +16558,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet, Riz, Crème, Moutarde).</t>
+          <t>Cuire le riz selon les indications du paquet.</t>
         </is>
       </c>
       <c r="C70" s="10" t="n"/>
@@ -16570,7 +16586,7 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Ajouter haricots verts et courge.</t>
+          <t>Ajouter la courge.</t>
         </is>
       </c>
       <c r="C72" s="10" t="n"/>
@@ -16616,7 +16632,7 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C76" s="9" t="n"/>
@@ -16986,7 +17002,7 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Poulet, Riz, Crème, Moutarde).</t>
+          <t>Cuire le riz selon les indications du paquet.</t>
         </is>
       </c>
       <c r="C95" s="10" t="n"/>
@@ -17014,7 +17030,7 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Ajouter haricots verts et poireaux.</t>
+          <t>Ajouter les poireaux.</t>
         </is>
       </c>
       <c r="C97" s="10" t="n"/>
@@ -17069,7 +17085,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -17375,7 +17391,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Haricots rouges, Riz, Tomates concassées).</t>
+          <t>Cuire le riz et émincer l’oignon.</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -17458,7 +17474,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -17794,7 +17810,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Pâtes, Lardons, Œufs, Parmesan).</t>
+          <t>Préparer les ingrédients.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -17877,7 +17893,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -18393,7 +18409,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Pâtes, Bœuf haché, Carottes, Épinards).</t>
+          <t>Préparer les ingrédients.</t>
         </is>
       </c>
       <c r="C25" s="10" t="n"/>
@@ -18476,7 +18492,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -18812,7 +18828,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Steak haché, Pain burger, Pommes de terre, Salade verte).</t>
+          <t>Préchauffer le four à 200 °C et couper les pommes de terre.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -18895,7 +18911,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -19231,7 +19247,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Pain de mie, Jambon, Fromage, Salade verte).</t>
+          <t>Préchauffer le four et préparer les tranches de pain.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -19314,7 +19330,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -19680,7 +19696,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Œufs, Lait, Jambon, Fromage).</t>
+          <t>Préparer les galettes et les ingrédients de la garniture.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -19763,7 +19779,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -20099,7 +20115,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Thon, Pâte brisée, Œufs, Salade verte).</t>
+          <t>Préchauffer le four à 180 °C et étaler la pâte.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -20182,7 +20198,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -20608,7 +20624,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Escalope de poulet, Œufs, Chapelure, Parmesan).</t>
+          <t>Préparer trois assiettes avec farine, œuf et chapelure.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -20691,7 +20707,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -20997,7 +21013,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Gnocchi, Gorgonzola, Noix).</t>
+          <t>Concasser les noix et couper le gorgonzola.</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -21080,7 +21096,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -21416,7 +21432,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Lasagnes, Épinards, Fromage, Salade verte).</t>
+          <t>Préchauffer le four à 180 °C.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -21499,7 +21515,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -21839,7 +21855,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz, Pois chiches, Lait de coco, Poivrons).</t>
+          <t>Cuire le riz et émincer les légumes.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -21913,7 +21929,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -22253,7 +22269,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz, Pois chiches, Lait de coco, Courgettes).</t>
+          <t>Cuire le riz et émincer les légumes.</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -22327,7 +22343,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C49" s="9" t="n"/>
@@ -22667,7 +22683,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz, Pois chiches, Lait de coco, Courge).</t>
+          <t>Cuire le riz et émincer les légumes.</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -22741,7 +22757,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C73" s="9" t="n"/>
@@ -23141,7 +23157,7 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz, Lait de coco, Asperges, Poivron).</t>
+          <t>Cuire le riz et émincer les légumes.</t>
         </is>
       </c>
       <c r="C93" s="10" t="n"/>
@@ -23195,6 +23211,454 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" style="7" min="1" max="1"/>
+    <col width="8" customWidth="1" style="7" min="2" max="2"/>
+    <col width="20" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16" customWidth="1" style="7" min="4" max="4"/>
+    <col width="10" customWidth="1" style="7" min="5" max="5"/>
+    <col width="20" customWidth="1" style="7" min="6" max="6"/>
+    <col width="34" customWidth="1" style="7" min="7" max="7"/>
+    <col width="38" customWidth="1" style="7" min="8" max="8"/>
+    <col width="38" customWidth="1" style="7" min="9" max="9"/>
+    <col width="34" customWidth="1" style="7" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>CATALOGUE DESSERTS</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>4.6.0</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
+      <c r="H1" s="12" t="n"/>
+      <c r="I1" s="12" t="n"/>
+      <c r="J1" s="12" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Icône</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Quantité pour 2</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Étape 1</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Étape 2</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Étape 3</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Étape 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Gâteau au chocolat</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>🍫</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Chocolat noir</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Faire fondre le chocolat.</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>Mélanger avec œufs, sucre et farine.</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>Verser dans un moule.</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>Cuire 20 min à 180 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Crêpes sucrées</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>🥞</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Mélanger farine, œufs et lait.</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>Laisser reposer la pâte 30 min.</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>Cuire les crêpes dans une poêle chaude.</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>Servir avec du sucre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Cake marbré</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>🍰</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Préparer une pâte à cake.</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>Séparer la pâte et ajouter le cacao.</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>Alterner les pâtes dans le moule.</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>Cuire 40 min à 170 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Cake citron-yaourt</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>🍋</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Yaourt</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Mélanger yaourt, œufs et sucre.</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>Ajouter farine, huile et citron.</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>Verser dans un moule.</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>Cuire 35 min à 180 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Riz au lait</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>🍚</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Riz rond</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Rincer le riz.</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>Chauffer le lait avec le sucre.</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>Ajouter le riz et cuire doucement 30 min.</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>Laisser tiédir avant de servir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Mousse au chocolat</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>🍮</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Chocolat noir</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Faire fondre le chocolat.</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>Séparer les blancs des jaunes.</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>Incorporer les blancs montés au chocolat.</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>Réserver 3 h au frais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Compote pomme-cannelle</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>🍎</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Pomme</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Éplucher et couper les pommes.</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>Ajouter un peu d’eau et la cannelle.</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>Cuire 20 min à feu doux.</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>Écraser ou mixer puis laisser refroidir.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -23224,7 +23688,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -23564,7 +24028,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz à risotto, Parmesan, Tomates, Petits pois).</t>
+          <t>Chauffer le bouillon dans une casserole.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -23638,7 +24102,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -23978,7 +24442,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz à risotto, Parmesan, Tomates, Courgettes).</t>
+          <t>Chauffer le bouillon dans une casserole.</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -24052,7 +24516,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C49" s="9" t="n"/>
@@ -24392,7 +24856,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz à risotto, Parmesan, Tomates, Courge).</t>
+          <t>Chauffer le bouillon dans une casserole.</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -24466,7 +24930,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C73" s="9" t="n"/>
@@ -24806,7 +25270,7 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Riz à risotto, Parmesan, Tomates, Poireaux).</t>
+          <t>Chauffer le bouillon dans une casserole.</t>
         </is>
       </c>
       <c r="C91" s="10" t="n"/>
@@ -24889,7 +25353,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -25229,7 +25693,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Quinoa, Œufs, Chapelure, Épinards).</t>
+          <t>Cuire le quinoa puis le laisser tiédir.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -25303,7 +25767,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -25643,7 +26107,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Quinoa, Œufs, Chapelure, Courgettes).</t>
+          <t>Cuire le quinoa puis le laisser tiédir.</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -25717,7 +26181,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C49" s="9" t="n"/>
@@ -26057,7 +26521,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Quinoa, Œufs, Chapelure, Courge).</t>
+          <t>Cuire le quinoa puis le laisser tiédir.</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -26131,7 +26595,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C73" s="9" t="n"/>
@@ -26471,7 +26935,7 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Quinoa, Œufs, Chapelure, Poireaux).</t>
+          <t>Cuire le quinoa puis le laisser tiédir.</t>
         </is>
       </c>
       <c r="C91" s="10" t="n"/>
@@ -26554,7 +27018,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -26894,7 +27358,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Cabillaud, Riz, Tomates, Épinards).</t>
+          <t>Cuire le riz puis préparer les légumes.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -26968,7 +27432,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -27308,7 +27772,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Cabillaud, Riz, Tomates, Courgettes).</t>
+          <t>Cuire le riz puis préparer les légumes.</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -27382,7 +27846,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C49" s="9" t="n"/>
@@ -27722,7 +28186,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Cabillaud, Riz, Tomates, Courge).</t>
+          <t>Cuire le riz puis préparer les légumes.</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -27796,7 +28260,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C73" s="9" t="n"/>
@@ -28136,7 +28600,7 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Cabillaud, Riz, Tomates, Poireaux).</t>
+          <t>Cuire le riz puis préparer les légumes.</t>
         </is>
       </c>
       <c r="C91" s="10" t="n"/>
@@ -28219,7 +28683,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -28529,7 +28993,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saumon, Quinoa, Petits pois).</t>
+          <t>Cuire le quinoa puis préparer les légumes.</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -28603,7 +29067,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
@@ -28913,7 +29377,7 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saumon, Quinoa, Courgettes).</t>
+          <t>Cuire le quinoa puis préparer les légumes.</t>
         </is>
       </c>
       <c r="C41" s="10" t="n"/>
@@ -28987,7 +29451,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C47" s="9" t="n"/>
@@ -29297,7 +29761,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saumon, Quinoa, Courge).</t>
+          <t>Cuire le quinoa puis préparer les légumes.</t>
         </is>
       </c>
       <c r="C64" s="10" t="n"/>
@@ -29371,7 +29835,7 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C70" s="9" t="n"/>
@@ -29681,7 +30145,7 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Saumon, Quinoa, Poireaux).</t>
+          <t>Cuire le quinoa puis préparer les légumes.</t>
         </is>
       </c>
       <c r="C87" s="10" t="n"/>
@@ -29764,7 +30228,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -30104,7 +30568,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pâte brisée, Œufs, Épinards).</t>
+          <t>Préchauffer le four à 180 °C et étaler la pâte.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -30118,7 +30582,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Préparer les épinards.</t>
+          <t>Préparer les légumes.</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -30178,7 +30642,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -30518,7 +30982,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pâte brisée, Œufs, Courgettes).</t>
+          <t>Préchauffer le four à 180 °C et étaler la pâte.</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
@@ -30532,7 +30996,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Préparer les épinards.</t>
+          <t>Préparer les légumes.</t>
         </is>
       </c>
       <c r="C44" s="10" t="n"/>
@@ -30592,7 +31056,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C49" s="9" t="n"/>
@@ -30932,7 +31396,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pâte brisée, Œufs, Courge).</t>
+          <t>Préchauffer le four à 180 °C et étaler la pâte.</t>
         </is>
       </c>
       <c r="C67" s="10" t="n"/>
@@ -30946,7 +31410,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Préparer les épinards.</t>
+          <t>Préparer les légumes.</t>
         </is>
       </c>
       <c r="C68" s="10" t="n"/>
@@ -31006,7 +31470,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C73" s="9" t="n"/>
@@ -31346,7 +31810,7 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pâte brisée, Œufs, Poireaux).</t>
+          <t>Préchauffer le four à 180 °C et étaler la pâte.</t>
         </is>
       </c>
       <c r="C91" s="10" t="n"/>
@@ -31360,7 +31824,7 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Préparer les épinards.</t>
+          <t>Préparer les légumes.</t>
         </is>
       </c>
       <c r="C92" s="10" t="n"/>
@@ -31429,7 +31893,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -31739,7 +32203,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pommes de terre, Épinards).</t>
+          <t>Préchauffer le four à 190 °C et couper les légumes.</t>
         </is>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -31753,7 +32217,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Cuire poireaux et pommes de terre.</t>
+          <t>Cuire les légumes et les pommes de terre.</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -31813,7 +32277,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
@@ -32123,7 +32587,7 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pommes de terre, Courgettes).</t>
+          <t>Préchauffer le four à 190 °C et couper les légumes.</t>
         </is>
       </c>
       <c r="C41" s="10" t="n"/>
@@ -32137,7 +32601,7 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Cuire poireaux et pommes de terre.</t>
+          <t>Cuire les légumes et les pommes de terre.</t>
         </is>
       </c>
       <c r="C42" s="10" t="n"/>
@@ -32197,7 +32661,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C47" s="9" t="n"/>
@@ -32507,7 +32971,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pommes de terre, Courge).</t>
+          <t>Préchauffer le four à 190 °C et couper les légumes.</t>
         </is>
       </c>
       <c r="C64" s="10" t="n"/>
@@ -32521,7 +32985,7 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Cuire poireaux et pommes de terre.</t>
+          <t>Cuire les légumes et les pommes de terre.</t>
         </is>
       </c>
       <c r="C65" s="10" t="n"/>
@@ -32581,7 +33045,7 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>4.5.0</t>
+          <t>4.6.0</t>
         </is>
       </c>
       <c r="C70" s="9" t="n"/>
@@ -32891,7 +33355,7 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Préparer le plan de travail et peser les ingrédients nécessaires (Fromage, Pommes de terre, Poireaux).</t>
+          <t>Préchauffer le four à 190 °C et couper les légumes.</t>
         </is>
       </c>
       <c r="C87" s="10" t="n"/>
@@ -32905,7 +33369,7 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Cuire poireaux et pommes de terre.</t>
+          <t>Cuire les légumes et les pommes de terre.</t>
         </is>
       </c>
       <c r="C88" s="10" t="n"/>

--- a/recettes.xlsx
+++ b/recettes.xlsx
@@ -79,7 +79,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00 €"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -158,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
@@ -176,6 +178,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -250,6 +253,461 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Microsoft Copilot</author>
+  </authors>
+  <commentList>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B39" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B47" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B52" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B53" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B56" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B58" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B59" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B60" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B61" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B62" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B63" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B64" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B65" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B66" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B67" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B71" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B72" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B73" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B74" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B75" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B76" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B77" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B78" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B79" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B80" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B81" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B82" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B83" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B84" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B85" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B86" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B87" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B88" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B89" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B90" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+    <comment ref="B91" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation indicative pour la région parisienne. Références générales : https://blog.ekip.app/prix-des-aliments-en-2026-etat-des-lieux-dun-panier-qui-pese-lourd/ et https://world-prices.com/fr/france/prix-nourriture</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -564,7 +1022,7 @@
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
     </row>
@@ -9931,7 +10389,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -10411,7 +10869,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -10847,7 +11305,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -11283,7 +11741,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -11719,7 +12177,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12139,7 +12597,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12575,7 +13033,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13011,7 +13469,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13447,7 +13905,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13867,7 +14325,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -14284,10 +14742,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -14301,7 +14759,13 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Estimations indicatives région parisienne</t>
         </is>
       </c>
     </row>
@@ -14330,11 +14794,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Avocat</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.5</v>
+          <t>Abricot</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>0.4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -14350,11 +14814,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boulgour</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.3</v>
+          <t>Asperges</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -14363,42 +14827,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cabillaud</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>28</v>
+          <t>Aubergine</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>1.35</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Poissonnerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Carottes</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.2</v>
+          <t>Avocat</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>1.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -14410,71 +14874,71 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Champignons</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>9</v>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>0.65</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>tranche</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Boucherie</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chocolat noir</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>14</v>
+          <t>Banane</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0.45</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Citron</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.65</v>
+          <t>Bœuf haché</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Boucherie</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Comté</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>24</v>
+          <t>Cabillaud</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>28</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -14483,18 +14947,18 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Crèmerie</t>
+          <t>Poissonnerie</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Courge</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.8</v>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>2.2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -14510,11 +14974,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Courgettes</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3.5</v>
+          <t>Carottes nouvelles</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>4.2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -14530,31 +14994,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Crème</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>4</v>
+          <t>Cerise</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>12</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Crèmerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Farine</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.2</v>
+          <t>Champignons</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>9</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -14563,18 +15027,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fromage</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>17.2</v>
+          <t>Chapelure</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>3.2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -14583,18 +15047,18 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Crèmerie</t>
+          <t>Épicerie</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Haricots rouges</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4</v>
+          <t>Chocolat noir</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -14610,15 +15074,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lait</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.2</v>
+          <t>Chèvre</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>22</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -14630,51 +15094,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>4.5</v>
+          <t>Citron</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>0.65</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lentilles corail</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>4.2</v>
+          <t>Clémentine</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>0.32</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lentilles vertes</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>3.8</v>
+          <t>Comté</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>24</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -14683,18 +15147,18 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Crèmerie</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Panais</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3.8</v>
+          <t>Courge</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>2.8</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -14710,31 +15174,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Parmesan</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>28</v>
+          <t>Courgette</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>1.1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Crèmerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Petits pois</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>4.5</v>
+          <t>Courgettes</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>3.5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -14750,31 +15214,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Poireaux</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>3</v>
+          <t>Crème</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Crèmerie</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Poivrons</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4.2</v>
+          <t>Escalope de poulet</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>18</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -14783,38 +15247,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Boucherie</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pomme</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0.48</v>
+          <t>Farine</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>1.2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pommes de terre</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>2</v>
+          <t>Fraise</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>12</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -14830,11 +15294,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Potiron</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2.8</v>
+          <t>Fromage</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>17.2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -14843,18 +15307,18 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Crèmerie</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Poulet</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>14</v>
+          <t>Gnocchi</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>4.5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -14863,18 +15327,18 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Boucherie</t>
+          <t>Épicerie</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pâtes</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>2.5</v>
+          <t>Gorgonzola</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>23</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -14883,18 +15347,18 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Crèmerie</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Quinoa</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>8</v>
+          <t>Haricots rouges</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -14910,11 +15374,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Riz</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3</v>
+          <t>Haricots verts</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>6.5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -14923,42 +15387,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Riz complet</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>3.2</v>
+          <t>Jambon</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>0.75</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Boucherie</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Riz rond</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3</v>
+          <t>Jus de citron</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>4.5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -14970,71 +15434,71 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Riz à risotto</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>4</v>
+          <t>Kiwi</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>0.6</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Salade verte</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1.4</v>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>1.2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Crèmerie</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Saumon</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>25</v>
+          <t>Lait de coco</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>4.5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Poissonnerie</t>
+          <t>Épicerie</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Semoule</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>2.8</v>
+          <t>Lardons</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>14</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -15043,18 +15507,18 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Boucherie</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>3</v>
+          <t>Lasagnes</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>4.2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -15070,31 +15534,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Yaourt</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0.55</v>
+          <t>Lentilles corail</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>4.2</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Crèmerie</t>
+          <t>Épicerie</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Épinards</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>5</v>
+          <t>Lentilles vertes</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>3.8</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -15103,25 +15567,1005 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Mandarine</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Mayonnaise</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Melon</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Moutarde</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Naan fromage</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Boulangerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Nectarine</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Noix</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Boulangerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Pain burger</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Boulangerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Pain complet</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Boulangerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Pain de mie</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Boulangerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Pamplemousse</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Parmesan</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Petits pois</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Poire</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Poireaux</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Pois chiches</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Poivron</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Poivrons</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Pomme</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Pommes de terre</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Potiron</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Poulet</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Boucherie</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Poulet rôti</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Boucherie</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Prune</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Pâte brisée</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Pâtes</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Pêche</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Quinoa</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Riz</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Riz rond</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Riz à risotto</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Salade romaine</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Salade verte</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sardines</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>boîte</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Poissonnerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Saucisse de Morteau</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Boucherie</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Saumon</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Poissonnerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Semoule</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Steak haché</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Boucherie</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Stracciatella</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Thon</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>boîte</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Poissonnerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Tomates</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Tomates concassées</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Yaourt</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Échalotes</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Épices guacamole</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>sachet</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Épinards</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>Œufs</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B91" s="7" t="n">
         <v>0.35</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>unité</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Crèmerie</t>
         </is>
@@ -15129,6 +16573,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -15157,7 +16602,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -15593,7 +17038,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -16029,7 +17474,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -16449,7 +17894,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -16855,7 +18300,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17261,7 +18706,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17667,7 +19112,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18057,7 +19502,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18493,7 +19938,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18929,7 +20374,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19365,7 +20810,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19831,7 +21276,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20251,7 +21696,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20657,7 +22102,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21063,7 +22508,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21469,7 +22914,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21859,7 +23304,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22265,7 +23710,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22671,7 +24116,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23077,7 +24522,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23467,7 +24912,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23943,7 +25388,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24409,7 +25854,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24795,7 +26240,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25181,7 +26626,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25567,7 +27012,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25953,7 +27398,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26369,7 +27814,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26905,7 +28350,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27411,7 +28856,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27797,7 +29242,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -28183,7 +29628,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -28599,7 +30044,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -29065,7 +30510,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -29661,7 +31106,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30077,7 +31522,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30493,7 +31938,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30939,7 +32384,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31355,7 +32800,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31861,7 +33306,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32247,7 +33692,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32659,7 +34104,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
     </row>
@@ -32855,7 +34300,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
     </row>
@@ -33055,7 +34500,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -33501,7 +34946,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
     </row>
@@ -33697,7 +35142,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
     </row>
@@ -33893,7 +35338,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
     </row>
@@ -34089,7 +35534,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
     </row>
@@ -34285,7 +35730,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
     </row>
@@ -34485,7 +35930,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -34921,7 +36366,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -35357,7 +36802,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.8.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>

--- a/recettes.xlsx
+++ b/recettes.xlsx
@@ -579,7 +579,7 @@
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -14325,10 +14325,9 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.9.0</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr"/>
+          <t>4.10.0</t>
+        </is>
+      </c>
       <c r="D1" t="inlineStr">
         <is>
           <t>Estimations indicatives région parisienne</t>
@@ -16848,7 +16847,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17265,7 +17264,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17682,7 +17681,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18099,7 +18098,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18486,7 +18485,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18873,7 +18872,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19260,7 +19259,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19647,7 +19646,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20064,7 +20063,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20481,7 +20480,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20898,7 +20897,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21345,7 +21344,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21762,7 +21761,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22149,7 +22148,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22536,7 +22535,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22923,7 +22922,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23310,7 +23309,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23727,7 +23726,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24144,7 +24143,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24561,7 +24560,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24978,7 +24977,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25511,7 +25510,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25958,7 +25957,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26371,7 +26370,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26784,7 +26783,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27257,7 +27256,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27700,7 +27699,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -28143,7 +28142,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -28706,7 +28705,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -29179,7 +29178,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -29532,7 +29531,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30035,7 +30034,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30418,7 +30417,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30865,7 +30864,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31338,7 +31337,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31811,7 +31810,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32224,7 +32223,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32637,7 +32636,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -33110,7 +33109,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -33613,7 +33612,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -34026,7 +34025,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -34465,7 +34464,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
     </row>
@@ -34811,7 +34810,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
     </row>
@@ -35131,7 +35130,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -35574,7 +35573,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
     </row>
@@ -35950,7 +35949,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
     </row>
@@ -36326,7 +36325,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
     </row>
@@ -36612,7 +36611,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
     </row>
@@ -36838,7 +36837,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
     </row>
@@ -37098,7 +37097,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -37575,7 +37574,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -38052,7 +38051,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.7.0</t>
+          <t>4.10.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>

--- a/recettes.xlsx
+++ b/recettes.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="19200" windowHeight="11240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semaines_Types" sheetId="1" state="visible" r:id="rId1"/>
@@ -73,7 +72,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dessert Compote pomme-cannelle" sheetId="64" state="visible" r:id="rId64"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -93,7 +92,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -105,13 +103,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -130,7 +129,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0023855B"/>
+        <fgColor rgb="FF23855B"/>
       </patternFill>
     </fill>
     <fill>
@@ -160,25 +159,21 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -261,6 +256,71 @@
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>Références culinaires générales consultées : https://www.marmiton.org/recettes/recette_ratatouille_23223.aspx ; https://www.marmiton.org/recettes/recette_salade-cesar_32442.aspx ; https://www.marmiton.org/recettes/recette_cake-marbre-au-chocolat_340772.aspx ; https://www.marmiton.org/recettes/recette_croque-monsieur_19208.aspx</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
+      </text>
+    </comment>
+    <comment ref="B102" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
+      </text>
+    </comment>
+    <comment ref="B103" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
+      </text>
+    </comment>
+    <comment ref="B104" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
+      </text>
+    </comment>
+    <comment ref="B105" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
+      </text>
+    </comment>
+    <comment ref="B106" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
+      </text>
+    </comment>
+    <comment ref="B107" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
+      </text>
+    </comment>
+    <comment ref="B108" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
+      </text>
+    </comment>
+    <comment ref="B109" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
+      </text>
+    </comment>
+    <comment ref="B110" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
+      </text>
+    </comment>
+    <comment ref="B111" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
+      </text>
+    </comment>
+    <comment ref="B112" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
+      </text>
+    </comment>
+    <comment ref="B113" authorId="0" shapeId="0">
+      <text>
+        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
       </text>
     </comment>
   </commentList>
@@ -557,7 +617,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M291"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -579,7 +639,7 @@
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1076,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Curry végétarien et riz, de saison (Poivrons)</t>
+          <t>Curry végétarien et riz, de saison (Asperges)</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1396,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Épinards)</t>
+          <t>Cabillaud et riz, de saison (Fenouil)</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1780,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Saumon et quinoa, de saison (Petits pois)</t>
+          <t>Saumon et quinoa, de saison (Fèves)</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1844,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Risotto au parmesan, de saison (Petits pois)</t>
+          <t>Risotto au parmesan, de saison (Artichaut)</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2228,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Curry végétarien et riz, de saison (Poivrons)</t>
+          <t>Curry végétarien et riz, de saison (Asperges)</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2484,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Risotto au parmesan, de saison (Petits pois)</t>
+          <t>Risotto au parmesan, de saison (Artichaut)</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2868,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa, de saison (Courgettes)</t>
+          <t>Galettes de légumes et quinoa, de saison (Aubergine)</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3060,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Curry végétarien et riz, de saison (Courgettes)</t>
+          <t>Curry végétarien et riz, de saison (Poivrons)</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3188,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Courgettes)</t>
+          <t>Cabillaud et riz, de saison (Tomates)</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3316,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Quiche au fromage, de saison (Courgettes)</t>
+          <t>Quiche au fromage, de saison (Aubergine)</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3444,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa, de saison (Courgettes)</t>
+          <t>Galettes de légumes et quinoa, de saison (Aubergine)</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3572,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Saumon et quinoa, de saison (Courgettes)</t>
+          <t>Saumon et quinoa, de saison (Poivrons)</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4276,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Curry végétarien et riz, de saison (Courgettes)</t>
+          <t>Curry végétarien et riz, de saison (Poivrons)</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4340,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Poulet rôti et pommes de terre, de saison (Courge)</t>
+          <t>Poulet rôti et pommes de terre, de saison (Panais)</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4596,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Saumon et quinoa, de saison (Courge)</t>
+          <t>Saumon et quinoa, de saison (Brocoli)</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4852,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa, de saison (Courge)</t>
+          <t>Galettes de légumes et quinoa, de saison (Betterave)</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4980,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Courge)</t>
+          <t>Cabillaud et riz, de saison (Chou-fleur)</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5300,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Poulet moutarde et riz, de saison (Courge)</t>
+          <t>Poulet moutarde et riz, de saison (Brocoli)</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5428,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Risotto au parmesan, de saison (Courge)</t>
+          <t>Risotto au parmesan, de saison (Champignons)</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5748,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Courge)</t>
+          <t>Cabillaud et riz, de saison (Chou-fleur)</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6388,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Saumon et quinoa, de saison (Poireaux)</t>
+          <t>Saumon et quinoa, de saison (Chou vert)</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6516,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Gratin au fromage, de saison (Poireaux)</t>
+          <t>Gratin au fromage, de saison (Chou-fleur)</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6580,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa, de saison (Poireaux)</t>
+          <t>Galettes de légumes et quinoa, de saison (Panais)</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6772,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Poireaux)</t>
+          <t>Cabillaud et riz, de saison (Endives)</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6900,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Gratin au fromage, de saison (Poireaux)</t>
+          <t>Gratin au fromage, de saison (Chou-fleur)</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6964,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Poulet moutarde et riz, de saison (Poireaux)</t>
+          <t>Poulet moutarde et riz, de saison (Carottes)</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7540,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Poireaux)</t>
+          <t>Cabillaud et riz, de saison (Endives)</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7860,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa, de saison (Poireaux)</t>
+          <t>Galettes de légumes et quinoa, de saison (Panais)</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9988,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -9946,7 +10006,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -9962,7 +10022,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Curry végétarien et riz, de saison (Pois chiches)</t>
+          <t>Curry végétarien et riz, de saison (Chou-fleur)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -9978,7 +10038,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Curry végétarien et riz Pois chiches</t>
+          <t>Curry végétarien et riz Chou-fleur</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -10217,11 +10277,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Carottes</t>
+          <t>Chou-fleur</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -10389,7 +10449,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cuire le riz et préparer les légumes.</t>
+          <t>Cuire le riz et émincer l’oignon.</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10469,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ajouter les légumes et les pois chiches, puis verser le lait de coco.</t>
+          <t>Ajouter chou-fleur et les pois chiches, puis verser le lait de coco.</t>
         </is>
       </c>
     </row>
@@ -10435,7 +10495,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -10453,7 +10513,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -10469,7 +10529,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Risotto au parmesan, de saison (Petits pois)</t>
+          <t>Risotto au parmesan, de saison (Artichaut)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -10485,7 +10545,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Risotto au parmesan Petits pois</t>
+          <t>Risotto au parmesan Artichaut</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -10694,11 +10754,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Petits pois</t>
+          <t>Artichaut</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -10836,7 +10896,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chauffer le bouillon et préparer le légume.</t>
+          <t>Préparer artichaut et chauffer le bouillon.</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10906,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon et le légume dans l’huile.</t>
+          <t>Faire revenir l’oignon et artichaut dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10942,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -10900,7 +10960,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -11283,7 +11343,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chauffer le bouillon et préparer le légume.</t>
+          <t>Préparer courgettes et chauffer le bouillon.</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11353,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon et le légume dans l’huile.</t>
+          <t>Faire revenir l’oignon et courgettes dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -11329,7 +11389,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -11347,7 +11407,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -11363,7 +11423,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Risotto au parmesan, de saison (Courge)</t>
+          <t>Risotto au parmesan, de saison (Champignons)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -11379,7 +11439,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Risotto au parmesan Courge</t>
+          <t>Risotto au parmesan Champignons</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -11588,7 +11648,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Courge</t>
+          <t>Champignons</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -11730,7 +11790,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chauffer le bouillon et préparer le légume.</t>
+          <t>Préparer champignons et chauffer le bouillon.</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11800,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon et le légume dans l’huile.</t>
+          <t>Faire revenir l’oignon et champignons dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -11776,7 +11836,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -11794,7 +11854,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12177,7 +12237,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chauffer le bouillon et préparer le légume.</t>
+          <t>Préparer poireaux et chauffer le bouillon.</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12247,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon et le légume dans l’huile.</t>
+          <t>Faire revenir l’oignon et poireaux dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -12223,7 +12283,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -12241,7 +12301,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12604,7 +12664,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Préparer le légume, le cuire si nécessaire et bien l’égoutter.</t>
+          <t>Préparer épinards, le cuire si nécessaire et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -12614,7 +12674,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger le quinoa, le légume, les œufs et la chapelure.</t>
+          <t>Mélanger le quinoa, épinards, les œufs et la chapelure.</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12700,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -12658,7 +12718,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12674,7 +12734,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa, de saison (Courgettes)</t>
+          <t>Galettes de légumes et quinoa, de saison (Aubergine)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -12690,7 +12750,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa Courgettes</t>
+          <t>Galettes de légumes et quinoa Aubergine</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -12929,7 +12989,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Courgettes</t>
+          <t>Aubergine</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -13021,7 +13081,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Préparer le légume, le cuire si nécessaire et bien l’égoutter.</t>
+          <t>Préparer aubergine, le cuire si nécessaire et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13091,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger le quinoa, le légume, les œufs et la chapelure.</t>
+          <t>Mélanger le quinoa, aubergine, les œufs et la chapelure.</t>
         </is>
       </c>
     </row>
@@ -13057,7 +13117,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -13075,7 +13135,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13091,7 +13151,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa, de saison (Courge)</t>
+          <t>Galettes de légumes et quinoa, de saison (Betterave)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -13107,7 +13167,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa Courge</t>
+          <t>Galettes de légumes et quinoa Betterave</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -13346,7 +13406,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Courge</t>
+          <t>Betterave</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -13438,7 +13498,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Préparer le légume, le cuire si nécessaire et bien l’égoutter.</t>
+          <t>Préparer betterave, le cuire si nécessaire et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -13448,7 +13508,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger le quinoa, le légume, les œufs et la chapelure.</t>
+          <t>Mélanger le quinoa, betterave, les œufs et la chapelure.</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13534,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -13492,7 +13552,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13508,7 +13568,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa, de saison (Poireaux)</t>
+          <t>Galettes de légumes et quinoa, de saison (Panais)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -13524,7 +13584,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Galettes de légumes et quinoa Poireaux</t>
+          <t>Galettes de légumes et quinoa Panais</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -13763,7 +13823,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Poireaux</t>
+          <t>Panais</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -13855,7 +13915,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Préparer le légume, le cuire si nécessaire et bien l’égoutter.</t>
+          <t>Préparer panais, le cuire si nécessaire et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -13865,7 +13925,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger le quinoa, le légume, les œufs et la chapelure.</t>
+          <t>Mélanger le quinoa, panais, les œufs et la chapelure.</t>
         </is>
       </c>
     </row>
@@ -13890,8 +13950,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -13909,7 +13969,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13925,7 +13985,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Épinards)</t>
+          <t>Cabillaud et riz, de saison (Fenouil)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -13941,7 +14001,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz Épinards</t>
+          <t>Cabillaud et riz Fenouil</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -14150,11 +14210,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tomates</t>
+          <t>Fenouil</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -14180,117 +14240,87 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Épinards</t>
+          <t>Huile d’olive</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Fond de placard</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Toutes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Huile d’olive</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Épicerie</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Fond de placard</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Toutes</t>
+          <t>ÉTAPES DE PRÉPARATION</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ÉTAPES DE PRÉPARATION</t>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Étape</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ordre</t>
-        </is>
+      <c r="A18" t="n">
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Étape</t>
+          <t>Cuire le riz.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cuire le riz et préparer les légumes.</t>
+          <t>Préparer puis faire revenir fenouil dans l’huile.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Faire revenir les tomates et le légume de saison dans l’huile.</t>
+          <t>Déposer le cabillaud, couvrir et cuire doucement.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
-        <is>
-          <t>Déposer le cabillaud, couvrir et cuire doucement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" t="inlineStr">
         <is>
           <t>Assaisonner et servir avec le riz.</t>
         </is>
@@ -14307,8 +14337,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E113"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -14325,7 +14355,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -14418,11 +14448,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -16813,6 +16843,306 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>Protéine</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Asperges</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>16</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Artichaut</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Fenouil</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Fèves</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>7</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Blettes</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Betterave</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Brocoli</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Champignons</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>7</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Chou-fleur</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Panais</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Endives</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Chou vert</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Légume</t>
         </is>
       </c>
     </row>
@@ -16828,8 +17158,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -16847,7 +17177,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -16863,7 +17193,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Courgettes)</t>
+          <t>Cabillaud et riz, de saison (Tomates)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -16879,7 +17209,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz Courgettes</t>
+          <t>Cabillaud et riz Tomates</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -17092,7 +17422,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -17118,117 +17448,87 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Courgettes</t>
+          <t>Huile d’olive</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Fond de placard</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>Toutes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Huile d’olive</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Épicerie</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Fond de placard</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Toutes</t>
+          <t>ÉTAPES DE PRÉPARATION</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ÉTAPES DE PRÉPARATION</t>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Étape</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ordre</t>
-        </is>
+      <c r="A18" t="n">
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Étape</t>
+          <t>Cuire le riz.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cuire le riz et préparer les légumes.</t>
+          <t>Préparer puis faire revenir tomates dans l’huile.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Faire revenir les tomates et le légume de saison dans l’huile.</t>
+          <t>Déposer le cabillaud, couvrir et cuire doucement.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
-        <is>
-          <t>Déposer le cabillaud, couvrir et cuire doucement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" t="inlineStr">
         <is>
           <t>Assaisonner et servir avec le riz.</t>
         </is>
@@ -17245,8 +17545,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -17264,7 +17564,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17280,7 +17580,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Courge)</t>
+          <t>Cabillaud et riz, de saison (Chou-fleur)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -17296,7 +17596,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz Courge</t>
+          <t>Cabillaud et riz Chou-fleur</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -17505,11 +17805,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tomates</t>
+          <t>Chou-fleur</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -17535,117 +17835,87 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Courge</t>
+          <t>Huile d’olive</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Fond de placard</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Autumn</t>
+          <t>Toutes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Huile d’olive</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Épicerie</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Fond de placard</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Toutes</t>
+          <t>ÉTAPES DE PRÉPARATION</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ÉTAPES DE PRÉPARATION</t>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Étape</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ordre</t>
-        </is>
+      <c r="A18" t="n">
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Étape</t>
+          <t>Cuire le riz.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cuire le riz et préparer les légumes.</t>
+          <t>Préparer puis faire revenir chou-fleur dans l’huile.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Faire revenir les tomates et le légume de saison dans l’huile.</t>
+          <t>Déposer le cabillaud, couvrir et cuire doucement.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
-        <is>
-          <t>Déposer le cabillaud, couvrir et cuire doucement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" t="inlineStr">
         <is>
           <t>Assaisonner et servir avec le riz.</t>
         </is>
@@ -17662,8 +17932,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -17681,7 +17951,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17697,7 +17967,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Poireaux)</t>
+          <t>Cabillaud et riz, de saison (Endives)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -17713,7 +17983,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz Poireaux</t>
+          <t>Cabillaud et riz Endives</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -17922,11 +18192,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tomates</t>
+          <t>Endives</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -17952,117 +18222,87 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Poireaux</t>
+          <t>Huile d’olive</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Fond de placard</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Winter</t>
+          <t>Toutes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Huile d’olive</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Épicerie</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Fond de placard</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Toutes</t>
+          <t>ÉTAPES DE PRÉPARATION</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ÉTAPES DE PRÉPARATION</t>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Étape</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ordre</t>
-        </is>
+      <c r="A18" t="n">
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Étape</t>
+          <t>Cuire le riz.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cuire le riz et préparer les légumes.</t>
+          <t>Préparer puis faire revenir endives dans l’huile.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Faire revenir les tomates et le légume de saison dans l’huile.</t>
+          <t>Déposer le cabillaud, couvrir et cuire doucement.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
-        <is>
-          <t>Déposer le cabillaud, couvrir et cuire doucement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" t="inlineStr">
         <is>
           <t>Assaisonner et servir avec le riz.</t>
         </is>
@@ -18080,7 +18320,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -18098,7 +18338,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18114,7 +18354,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Saumon et quinoa, de saison (Petits pois)</t>
+          <t>Saumon et quinoa, de saison (Fèves)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -18130,7 +18370,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Saumon et quinoa Petits pois</t>
+          <t>Saumon et quinoa Fèves</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -18339,11 +18579,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Petits pois</t>
+          <t>Fèves</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -18431,7 +18671,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préparer puis faire revenir le légume dans l’huile.</t>
+          <t>Préparer puis faire revenir fèves dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18691,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Servir le saumon avec le quinoa et le légume.</t>
+          <t>Servir le saumon avec le quinoa et fèves.</t>
         </is>
       </c>
     </row>
@@ -18467,7 +18707,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -18485,7 +18725,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18501,7 +18741,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Saumon et quinoa, de saison (Courgettes)</t>
+          <t>Saumon et quinoa, de saison (Poivrons)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -18517,7 +18757,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Saumon et quinoa Courgettes</t>
+          <t>Saumon et quinoa Poivrons</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -18726,7 +18966,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Courgettes</t>
+          <t>Poivrons</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -18818,7 +19058,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préparer puis faire revenir le légume dans l’huile.</t>
+          <t>Préparer puis faire revenir poivrons dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -18838,7 +19078,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Servir le saumon avec le quinoa et le légume.</t>
+          <t>Servir le saumon avec le quinoa et poivrons.</t>
         </is>
       </c>
     </row>
@@ -18854,7 +19094,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -18872,7 +19112,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18888,7 +19128,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Saumon et quinoa, de saison (Courge)</t>
+          <t>Saumon et quinoa, de saison (Brocoli)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -18904,7 +19144,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Saumon et quinoa Courge</t>
+          <t>Saumon et quinoa Brocoli</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -19113,7 +19353,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Courge</t>
+          <t>Brocoli</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -19205,7 +19445,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préparer puis faire revenir le légume dans l’huile.</t>
+          <t>Préparer puis faire revenir brocoli dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -19225,7 +19465,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Servir le saumon avec le quinoa et le légume.</t>
+          <t>Servir le saumon avec le quinoa et brocoli.</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19481,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -19259,7 +19499,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19275,7 +19515,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Saumon et quinoa, de saison (Poireaux)</t>
+          <t>Saumon et quinoa, de saison (Chou vert)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -19291,7 +19531,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Saumon et quinoa Poireaux</t>
+          <t>Saumon et quinoa Chou vert</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -19500,7 +19740,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Poireaux</t>
+          <t>Chou vert</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -19592,7 +19832,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préparer puis faire revenir le légume dans l’huile.</t>
+          <t>Préparer puis faire revenir chou vert dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -19612,7 +19852,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Servir le saumon avec le quinoa et le légume.</t>
+          <t>Servir le saumon avec le quinoa et chou vert.</t>
         </is>
       </c>
     </row>
@@ -19628,7 +19868,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -19646,7 +19886,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20009,7 +20249,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Précuire le légume et l’égoutter soigneusement.</t>
+          <t>Précuire épinards et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -20019,7 +20259,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger les œufs et la crème, puis ajouter le légume et le fromage.</t>
+          <t>Mélanger les œufs et la crème, puis ajouter épinards et le fromage.</t>
         </is>
       </c>
     </row>
@@ -20045,7 +20285,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -20063,7 +20303,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20079,7 +20319,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Quiche au fromage, de saison (Courgettes)</t>
+          <t>Quiche au fromage, de saison (Aubergine)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -20095,7 +20335,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Quiche au fromage Courgettes</t>
+          <t>Quiche au fromage Aubergine</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -20334,7 +20574,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Courgettes</t>
+          <t>Aubergine</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -20426,7 +20666,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Précuire le légume et l’égoutter soigneusement.</t>
+          <t>Précuire aubergine et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -20436,7 +20676,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger les œufs et la crème, puis ajouter le légume et le fromage.</t>
+          <t>Mélanger les œufs et la crème, puis ajouter aubergine et le fromage.</t>
         </is>
       </c>
     </row>
@@ -20462,7 +20702,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -20480,7 +20720,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20496,7 +20736,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Quiche au fromage, de saison (Courge)</t>
+          <t>Quiche au fromage, de saison (Poireaux)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -20512,7 +20752,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Quiche au fromage Courge</t>
+          <t>Quiche au fromage Poireaux</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -20751,7 +20991,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Courge</t>
+          <t>Poireaux</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -20843,7 +21083,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Précuire le légume et l’égoutter soigneusement.</t>
+          <t>Précuire poireaux et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -20853,7 +21093,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger les œufs et la crème, puis ajouter le légume et le fromage.</t>
+          <t>Mélanger les œufs et la crème, puis ajouter poireaux et le fromage.</t>
         </is>
       </c>
     </row>
@@ -20879,7 +21119,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -20897,7 +21137,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21280,7 +21520,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cuire le riz selon les indications du paquet.</t>
+          <t>Cuire le riz et préparer petits pois.</t>
         </is>
       </c>
     </row>
@@ -21300,7 +21540,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ajouter le légume, puis la moutarde et la crème.</t>
+          <t>Ajouter petits pois, puis la moutarde et la crème.</t>
         </is>
       </c>
     </row>
@@ -21326,7 +21566,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -21344,7 +21584,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21360,7 +21600,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Quiche au fromage, de saison (Poireaux)</t>
+          <t>Quiche au fromage, de saison (Chou-fleur)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -21376,7 +21616,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Quiche au fromage Poireaux</t>
+          <t>Quiche au fromage Chou-fleur</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -21615,7 +21855,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Poireaux</t>
+          <t>Chou-fleur</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -21707,7 +21947,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Précuire le légume et l’égoutter soigneusement.</t>
+          <t>Précuire chou-fleur et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -21717,7 +21957,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger les œufs et la crème, puis ajouter le légume et le fromage.</t>
+          <t>Mélanger les œufs et la crème, puis ajouter chou-fleur et le fromage.</t>
         </is>
       </c>
     </row>
@@ -21743,7 +21983,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -21761,7 +22001,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21777,7 +22017,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Gratin au fromage, de saison (Épinards)</t>
+          <t>Gratin au fromage, de saison (Blettes)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -21793,7 +22033,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Gratin au fromage Épinards</t>
+          <t>Gratin au fromage Blettes</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -22002,7 +22242,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Épinards</t>
+          <t>Blettes</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -22084,7 +22324,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Préchauffer le four à 190 °C et préparer les légumes.</t>
+          <t>Préchauffer le four à 190 °C.</t>
         </is>
       </c>
     </row>
@@ -22094,7 +22334,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Précuire les pommes de terre et le légume de saison.</t>
+          <t>Précuire les pommes de terre et blettes.</t>
         </is>
       </c>
     </row>
@@ -22104,7 +22344,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Disposer dans un plat, puis ajouter la crème et le fromage.</t>
+          <t>Disposer dans un plat, puis ajouter la crème et le fromage sur blettes.</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22370,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -22148,7 +22388,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22164,7 +22404,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Gratin au fromage, de saison (Courgettes)</t>
+          <t>Gratin au fromage, de saison (Aubergine)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -22180,7 +22420,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Gratin au fromage Courgettes</t>
+          <t>Gratin au fromage Aubergine</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -22389,7 +22629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Courgettes</t>
+          <t>Aubergine</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -22471,7 +22711,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Préchauffer le four à 190 °C et préparer les légumes.</t>
+          <t>Préchauffer le four à 190 °C.</t>
         </is>
       </c>
     </row>
@@ -22481,7 +22721,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Précuire les pommes de terre et le légume de saison.</t>
+          <t>Précuire les pommes de terre et aubergine.</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22731,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Disposer dans un plat, puis ajouter la crème et le fromage.</t>
+          <t>Disposer dans un plat, puis ajouter la crème et le fromage sur aubergine.</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22757,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -22535,7 +22775,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22858,7 +23098,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Préchauffer le four à 190 °C et préparer les légumes.</t>
+          <t>Préchauffer le four à 190 °C.</t>
         </is>
       </c>
     </row>
@@ -22868,7 +23108,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Précuire les pommes de terre et le légume de saison.</t>
+          <t>Précuire les pommes de terre et courge.</t>
         </is>
       </c>
     </row>
@@ -22878,7 +23118,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Disposer dans un plat, puis ajouter la crème et le fromage.</t>
+          <t>Disposer dans un plat, puis ajouter la crème et le fromage sur courge.</t>
         </is>
       </c>
     </row>
@@ -22904,7 +23144,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -22922,7 +23162,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22938,7 +23178,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Gratin au fromage, de saison (Poireaux)</t>
+          <t>Gratin au fromage, de saison (Chou-fleur)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -22954,7 +23194,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Gratin au fromage Poireaux</t>
+          <t>Gratin au fromage Chou-fleur</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -23163,7 +23403,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Poireaux</t>
+          <t>Chou-fleur</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -23245,7 +23485,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Préchauffer le four à 190 °C et préparer les légumes.</t>
+          <t>Préchauffer le four à 190 °C.</t>
         </is>
       </c>
     </row>
@@ -23255,7 +23495,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Précuire les pommes de terre et le légume de saison.</t>
+          <t>Précuire les pommes de terre et chou-fleur.</t>
         </is>
       </c>
     </row>
@@ -23265,7 +23505,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Disposer dans un plat, puis ajouter la crème et le fromage.</t>
+          <t>Disposer dans un plat, puis ajouter la crème et le fromage sur chou-fleur.</t>
         </is>
       </c>
     </row>
@@ -23291,7 +23531,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -23309,7 +23549,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23662,7 +23902,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préchauffer le four à 190 °C et couper les légumes.</t>
+          <t>Préchauffer le four à 190 °C.</t>
         </is>
       </c>
     </row>
@@ -23672,7 +23912,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mélanger les pommes de terre et le légume avec l’huile et les herbes.</t>
+          <t>Couper les pommes de terre et carottes nouvelles, puis mélanger avec l’huile et les herbes.</t>
         </is>
       </c>
     </row>
@@ -23692,7 +23932,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cuire jusqu’à cuisson complète, en ajoutant les courgettes à mi-cuisson en été.</t>
+          <t>Cuire jusqu’à cuisson complète en surveillant la cuisson de carottes nouvelles.</t>
         </is>
       </c>
     </row>
@@ -23708,7 +23948,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -23726,7 +23966,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24079,7 +24319,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préchauffer le four à 190 °C et couper les légumes.</t>
+          <t>Préchauffer le four à 190 °C.</t>
         </is>
       </c>
     </row>
@@ -24089,7 +24329,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mélanger les pommes de terre et le légume avec l’huile et les herbes.</t>
+          <t>Couper les pommes de terre et courgettes, puis mélanger avec l’huile et les herbes.</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24349,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cuire jusqu’à cuisson complète, en ajoutant les courgettes à mi-cuisson en été.</t>
+          <t>Cuire jusqu’à cuisson complète en surveillant la cuisson de courgettes.</t>
         </is>
       </c>
     </row>
@@ -24125,7 +24365,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -24143,7 +24383,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24159,7 +24399,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Poulet rôti et pommes de terre, de saison (Courge)</t>
+          <t>Poulet rôti et pommes de terre, de saison (Panais)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -24175,7 +24415,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Poulet rôti et pommes de terre Courge</t>
+          <t>Poulet rôti et pommes de terre Panais</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -24384,7 +24624,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Courge</t>
+          <t>Panais</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -24496,7 +24736,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préchauffer le four à 190 °C et couper les légumes.</t>
+          <t>Préchauffer le four à 190 °C.</t>
         </is>
       </c>
     </row>
@@ -24506,7 +24746,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mélanger les pommes de terre et le légume avec l’huile et les herbes.</t>
+          <t>Couper les pommes de terre et panais, puis mélanger avec l’huile et les herbes.</t>
         </is>
       </c>
     </row>
@@ -24526,7 +24766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cuire jusqu’à cuisson complète, en ajoutant les courgettes à mi-cuisson en été.</t>
+          <t>Cuire jusqu’à cuisson complète en surveillant la cuisson de panais.</t>
         </is>
       </c>
     </row>
@@ -24542,7 +24782,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -24560,7 +24800,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24913,7 +25153,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préchauffer le four à 190 °C et couper les légumes.</t>
+          <t>Préchauffer le four à 190 °C.</t>
         </is>
       </c>
     </row>
@@ -24923,7 +25163,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mélanger les pommes de terre et le légume avec l’huile et les herbes.</t>
+          <t>Couper les pommes de terre et carottes, puis mélanger avec l’huile et les herbes.</t>
         </is>
       </c>
     </row>
@@ -24943,7 +25183,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cuire jusqu’à cuisson complète, en ajoutant les courgettes à mi-cuisson en été.</t>
+          <t>Cuire jusqu’à cuisson complète en surveillant la cuisson de carottes.</t>
         </is>
       </c>
     </row>
@@ -24959,7 +25199,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -24977,7 +25217,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25492,7 +25732,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -25510,7 +25750,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25893,7 +26133,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cuire le riz selon les indications du paquet.</t>
+          <t>Cuire le riz et préparer haricots verts.</t>
         </is>
       </c>
     </row>
@@ -25913,7 +26153,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ajouter le légume, puis la moutarde et la crème.</t>
+          <t>Ajouter haricots verts, puis la moutarde et la crème.</t>
         </is>
       </c>
     </row>
@@ -25939,7 +26179,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -25957,7 +26197,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26352,7 +26592,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -26370,7 +26610,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26765,7 +27005,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -26783,7 +27023,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27238,7 +27478,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -27256,7 +27496,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27681,7 +27921,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -27699,7 +27939,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -28124,7 +28364,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -28142,7 +28382,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -28687,7 +28927,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -28705,7 +28945,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -29160,7 +29400,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -29178,7 +29418,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -29513,7 +29753,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -29531,7 +29771,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30016,7 +30256,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -30034,7 +30274,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30399,7 +30639,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -30417,7 +30657,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30433,7 +30673,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Poulet moutarde et riz, de saison (Courge)</t>
+          <t>Poulet moutarde et riz, de saison (Brocoli)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -30449,7 +30689,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Poulet moutarde et riz Courge</t>
+          <t>Poulet moutarde et riz Brocoli</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -30718,7 +30958,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Courge</t>
+          <t>Brocoli</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -30800,7 +31040,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cuire le riz selon les indications du paquet.</t>
+          <t>Cuire le riz et préparer brocoli.</t>
         </is>
       </c>
     </row>
@@ -30820,7 +31060,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ajouter le légume, puis la moutarde et la crème.</t>
+          <t>Ajouter brocoli, puis la moutarde et la crème.</t>
         </is>
       </c>
     </row>
@@ -30846,7 +31086,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -30864,7 +31104,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31319,7 +31559,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -31337,7 +31577,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31792,7 +32032,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -31810,7 +32050,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32205,7 +32445,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -32223,7 +32463,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32618,7 +32858,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -32636,7 +32876,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -33091,7 +33331,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -33109,7 +33349,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -33594,7 +33834,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -33612,7 +33852,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -34007,7 +34247,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -34025,7 +34265,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -34450,7 +34690,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
@@ -34464,7 +34704,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
     </row>
@@ -34796,7 +35036,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
@@ -34810,7 +35050,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
     </row>
@@ -35112,7 +35352,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -35130,7 +35370,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -35146,7 +35386,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Poulet moutarde et riz, de saison (Poireaux)</t>
+          <t>Poulet moutarde et riz, de saison (Carottes)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -35162,7 +35402,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Poulet moutarde et riz Poireaux</t>
+          <t>Poulet moutarde et riz Carottes</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -35431,7 +35671,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Poireaux</t>
+          <t>Carottes</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -35513,7 +35753,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cuire le riz selon les indications du paquet.</t>
+          <t>Cuire le riz et préparer carottes.</t>
         </is>
       </c>
     </row>
@@ -35533,7 +35773,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ajouter le légume, puis la moutarde et la crème.</t>
+          <t>Ajouter carottes, puis la moutarde et la crème.</t>
         </is>
       </c>
     </row>
@@ -35559,7 +35799,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
@@ -35573,7 +35813,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
     </row>
@@ -35935,7 +36175,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
@@ -35949,7 +36189,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
     </row>
@@ -36311,7 +36551,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
@@ -36325,7 +36565,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
     </row>
@@ -36597,7 +36837,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
@@ -36611,7 +36851,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
     </row>
@@ -36823,7 +37063,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
@@ -36837,7 +37077,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
     </row>
@@ -37079,7 +37319,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -37097,7 +37337,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -37113,7 +37353,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Curry végétarien et riz, de saison (Poivrons)</t>
+          <t>Curry végétarien et riz, de saison (Asperges)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -37129,7 +37369,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Curry végétarien et riz Poivrons</t>
+          <t>Curry végétarien et riz Asperges</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -37368,7 +37608,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Poivrons</t>
+          <t>Asperges</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -37510,7 +37750,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cuire le riz et préparer les légumes.</t>
+          <t>Cuire le riz et émincer l’oignon.</t>
         </is>
       </c>
     </row>
@@ -37530,7 +37770,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ajouter les légumes et les pois chiches, puis verser le lait de coco.</t>
+          <t>Ajouter asperges et les pois chiches, puis verser le lait de coco.</t>
         </is>
       </c>
     </row>
@@ -37556,7 +37796,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -37574,7 +37814,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -37590,7 +37830,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Curry végétarien et riz, de saison (Courgettes)</t>
+          <t>Curry végétarien et riz, de saison (Poivrons)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -37606,7 +37846,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Curry végétarien et riz Courgettes</t>
+          <t>Curry végétarien et riz Poivrons</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -37845,7 +38085,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Courgettes</t>
+          <t>Poivrons</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -37987,7 +38227,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cuire le riz et préparer les légumes.</t>
+          <t>Cuire le riz et émincer l’oignon.</t>
         </is>
       </c>
     </row>
@@ -38007,7 +38247,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ajouter les légumes et les pois chiches, puis verser le lait de coco.</t>
+          <t>Ajouter poivrons et les pois chiches, puis verser le lait de coco.</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38273,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
@@ -38051,7 +38291,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.10.0</t>
+          <t>4.11.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -38464,7 +38704,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cuire le riz et préparer les légumes.</t>
+          <t>Cuire le riz et émincer l’oignon.</t>
         </is>
       </c>
     </row>
@@ -38484,7 +38724,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ajouter les légumes et les pois chiches, puis verser le lait de coco.</t>
+          <t>Ajouter courge et les pois chiches, puis verser le lait de coco.</t>
         </is>
       </c>
     </row>

--- a/recettes.xlsx
+++ b/recettes.xlsx
@@ -256,71 +256,6 @@
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>Références culinaires générales consultées : https://www.marmiton.org/recettes/recette_ratatouille_23223.aspx ; https://www.marmiton.org/recettes/recette_salade-cesar_32442.aspx ; https://www.marmiton.org/recettes/recette_cake-marbre-au-chocolat_340772.aspx ; https://www.marmiton.org/recettes/recette_croque-monsieur_19208.aspx</t>
-      </text>
-    </comment>
-    <comment ref="B5" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
-      </text>
-    </comment>
-    <comment ref="B102" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
-      </text>
-    </comment>
-    <comment ref="B103" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
-      </text>
-    </comment>
-    <comment ref="B104" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
-      </text>
-    </comment>
-    <comment ref="B105" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
-      </text>
-    </comment>
-    <comment ref="B106" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
-      </text>
-    </comment>
-    <comment ref="B107" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
-      </text>
-    </comment>
-    <comment ref="B108" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
-      </text>
-    </comment>
-    <comment ref="B109" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
-      </text>
-    </comment>
-    <comment ref="B110" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
-      </text>
-    </comment>
-    <comment ref="B111" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
-      </text>
-    </comment>
-    <comment ref="B112" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
-      </text>
-    </comment>
-    <comment ref="B113" authorId="0" shapeId="0">
-      <text>
-        <t>Estimation de détail Paris fondée sur les cours de gros Rungis du 28/08/2026, avec majoration indicative de vente au détail. Sources : https://rnm.franceagrimer.fr/prix?M0123:MARCHE ; https://www.foodotrends.com/categorie/legumes</t>
       </text>
     </comment>
   </commentList>
@@ -639,7 +574,7 @@
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -10006,7 +9941,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -10307,15 +10242,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Poireaux</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>180</v>
+        <v>0.25</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10325,7 +10260,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Complément</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -10337,25 +10272,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Curry</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>c. à café</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Fond de placard</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -10367,15 +10302,15 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Curry</t>
+          <t>Huile d’olive</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>c. à café</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10397,87 +10332,57 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Huile d’olive</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>10</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Épicerie</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Fond de placard</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Toutes</t>
+          <t>ÉTAPES DE PRÉPARATION</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ÉTAPES DE PRÉPARATION</t>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Étape</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Ordre</t>
-        </is>
+      <c r="A21" t="n">
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Étape</t>
+          <t>Cuire le riz et émincer l’oignon.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cuire le riz et émincer l’oignon.</t>
+          <t>Faire revenir l’oignon avec l’huile et le curry.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon avec l’huile et le curry.</t>
+          <t>Ajouter le chou-fleur et les pois chiches, puis verser le lait de coco.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
-        <is>
-          <t>Ajouter chou-fleur et les pois chiches, puis verser le lait de coco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" t="inlineStr">
         <is>
           <t>Mijoter 15 à 20 minutes et servir avec le riz.</t>
         </is>
@@ -10513,7 +10418,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -10896,7 +10801,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Préparer artichaut et chauffer le bouillon.</t>
+          <t>Préparer le artichaut et chauffer le bouillon.</t>
         </is>
       </c>
     </row>
@@ -10906,7 +10811,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon et artichaut dans l’huile.</t>
+          <t>Faire revenir l’oignon et le artichaut dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10865,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -11343,7 +11248,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Préparer courgettes et chauffer le bouillon.</t>
+          <t>Préparer le courgettes et chauffer le bouillon.</t>
         </is>
       </c>
     </row>
@@ -11353,7 +11258,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon et courgettes dans l’huile.</t>
+          <t>Faire revenir l’oignon et le courgettes dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -11407,7 +11312,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -11790,7 +11695,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Préparer champignons et chauffer le bouillon.</t>
+          <t>Préparer le champignons et chauffer le bouillon.</t>
         </is>
       </c>
     </row>
@@ -11800,7 +11705,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon et champignons dans l’huile.</t>
+          <t>Faire revenir l’oignon et le champignons dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -11854,7 +11759,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12237,7 +12142,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Préparer poireaux et chauffer le bouillon.</t>
+          <t>Préparer le poireaux et chauffer le bouillon.</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12152,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Faire revenir l’oignon et poireaux dans l’huile.</t>
+          <t>Faire revenir l’oignon et le poireaux dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -12301,7 +12206,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12664,7 +12569,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Préparer épinards, le cuire si nécessaire et bien l’égoutter.</t>
+          <t>Préparer le épinards, le cuire si nécessaire et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12579,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger le quinoa, épinards, les œufs et la chapelure.</t>
+          <t>Mélanger le quinoa, le épinards, les œufs et la chapelure.</t>
         </is>
       </c>
     </row>
@@ -12718,7 +12623,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13081,7 +12986,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Préparer aubergine, le cuire si nécessaire et bien l’égoutter.</t>
+          <t>Préparer le aubergine, le cuire si nécessaire et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -13091,7 +12996,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger le quinoa, aubergine, les œufs et la chapelure.</t>
+          <t>Mélanger le quinoa, le aubergine, les œufs et la chapelure.</t>
         </is>
       </c>
     </row>
@@ -13135,7 +13040,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13498,7 +13403,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Préparer betterave, le cuire si nécessaire et bien l’égoutter.</t>
+          <t>Préparer le betterave, le cuire si nécessaire et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -13508,7 +13413,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger le quinoa, betterave, les œufs et la chapelure.</t>
+          <t>Mélanger le quinoa, le betterave, les œufs et la chapelure.</t>
         </is>
       </c>
     </row>
@@ -13552,7 +13457,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13915,7 +13820,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Préparer panais, le cuire si nécessaire et bien l’égoutter.</t>
+          <t>Préparer le panais, le cuire si nécessaire et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -13925,7 +13830,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger le quinoa, panais, les œufs et la chapelure.</t>
+          <t>Mélanger le quinoa, le panais, les œufs et la chapelure.</t>
         </is>
       </c>
     </row>
@@ -13969,7 +13874,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -14302,7 +14207,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préparer puis faire revenir fenouil dans l’huile.</t>
+          <t>Préparer puis faire revenir le fenouil dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14260,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -17177,7 +17082,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17510,7 +17415,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préparer puis faire revenir tomates dans l’huile.</t>
+          <t>Préparer puis faire revenir le tomates dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -17564,7 +17469,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17897,7 +17802,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préparer puis faire revenir chou-fleur dans l’huile.</t>
+          <t>Préparer puis faire revenir le chou-fleur dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -17951,7 +17856,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18284,7 +18189,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préparer puis faire revenir endives dans l’huile.</t>
+          <t>Préparer puis faire revenir le endives dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -18338,7 +18243,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18671,7 +18576,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préparer puis faire revenir fèves dans l’huile.</t>
+          <t>Préparer puis faire revenir le fèves dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -18691,7 +18596,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Servir le saumon avec le quinoa et fèves.</t>
+          <t>Servir le saumon avec le quinoa et le fèves.</t>
         </is>
       </c>
     </row>
@@ -18725,7 +18630,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19058,7 +18963,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préparer puis faire revenir poivrons dans l’huile.</t>
+          <t>Préparer puis faire revenir le poivrons dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -19078,7 +18983,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Servir le saumon avec le quinoa et poivrons.</t>
+          <t>Servir le saumon avec le quinoa et le poivrons.</t>
         </is>
       </c>
     </row>
@@ -19112,7 +19017,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19445,7 +19350,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préparer puis faire revenir brocoli dans l’huile.</t>
+          <t>Préparer puis faire revenir le brocoli dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -19465,7 +19370,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Servir le saumon avec le quinoa et brocoli.</t>
+          <t>Servir le saumon avec le quinoa et le brocoli.</t>
         </is>
       </c>
     </row>
@@ -19499,7 +19404,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19832,7 +19737,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Préparer puis faire revenir chou vert dans l’huile.</t>
+          <t>Préparer puis faire revenir le chou vert dans l’huile.</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19757,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Servir le saumon avec le quinoa et chou vert.</t>
+          <t>Servir le saumon avec le quinoa et le chou vert.</t>
         </is>
       </c>
     </row>
@@ -19886,7 +19791,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20249,7 +20154,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Précuire épinards et bien l’égoutter.</t>
+          <t>Précuire le épinards et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -20259,7 +20164,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger les œufs et la crème, puis ajouter épinards et le fromage.</t>
+          <t>Mélanger les œufs et la crème, puis ajouter le épinards et le fromage.</t>
         </is>
       </c>
     </row>
@@ -20303,7 +20208,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20666,7 +20571,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Précuire aubergine et bien l’égoutter.</t>
+          <t>Précuire le aubergine et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -20676,7 +20581,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger les œufs et la crème, puis ajouter aubergine et le fromage.</t>
+          <t>Mélanger les œufs et la crème, puis ajouter le aubergine et le fromage.</t>
         </is>
       </c>
     </row>
@@ -20720,7 +20625,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21083,7 +20988,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Précuire poireaux et bien l’égoutter.</t>
+          <t>Précuire le poireaux et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -21093,7 +20998,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger les œufs et la crème, puis ajouter poireaux et le fromage.</t>
+          <t>Mélanger les œufs et la crème, puis ajouter le poireaux et le fromage.</t>
         </is>
       </c>
     </row>
@@ -21137,7 +21042,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21520,7 +21425,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cuire le riz et préparer petits pois.</t>
+          <t>Cuire le riz et préparer les petits pois.</t>
         </is>
       </c>
     </row>
@@ -21540,7 +21445,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ajouter petits pois, puis la moutarde et la crème.</t>
+          <t>Ajouter les petits pois, puis la moutarde et la crème.</t>
         </is>
       </c>
     </row>
@@ -21584,7 +21489,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21947,7 +21852,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Précuire chou-fleur et bien l’égoutter.</t>
+          <t>Précuire le chou-fleur et bien l’égoutter.</t>
         </is>
       </c>
     </row>
@@ -21957,7 +21862,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mélanger les œufs et la crème, puis ajouter chou-fleur et le fromage.</t>
+          <t>Mélanger les œufs et la crème, puis ajouter le chou-fleur et le fromage.</t>
         </is>
       </c>
     </row>
@@ -22001,7 +21906,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22334,7 +22239,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Précuire les pommes de terre et blettes.</t>
+          <t>Précuire les pommes de terre et le blettes.</t>
         </is>
       </c>
     </row>
@@ -22344,7 +22249,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Disposer dans un plat, puis ajouter la crème et le fromage sur blettes.</t>
+          <t>Disposer dans un plat, puis ajouter la crème et le fromage sur le blettes.</t>
         </is>
       </c>
     </row>
@@ -22388,7 +22293,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22721,7 +22626,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Précuire les pommes de terre et aubergine.</t>
+          <t>Précuire les pommes de terre et le aubergine.</t>
         </is>
       </c>
     </row>
@@ -22731,7 +22636,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Disposer dans un plat, puis ajouter la crème et le fromage sur aubergine.</t>
+          <t>Disposer dans un plat, puis ajouter la crème et le fromage sur le aubergine.</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22680,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23108,7 +23013,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Précuire les pommes de terre et courge.</t>
+          <t>Précuire les pommes de terre et le courge.</t>
         </is>
       </c>
     </row>
@@ -23118,7 +23023,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Disposer dans un plat, puis ajouter la crème et le fromage sur courge.</t>
+          <t>Disposer dans un plat, puis ajouter la crème et le fromage sur le courge.</t>
         </is>
       </c>
     </row>
@@ -23162,7 +23067,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23495,7 +23400,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Précuire les pommes de terre et chou-fleur.</t>
+          <t>Précuire les pommes de terre et le chou-fleur.</t>
         </is>
       </c>
     </row>
@@ -23505,7 +23410,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Disposer dans un plat, puis ajouter la crème et le fromage sur chou-fleur.</t>
+          <t>Disposer dans un plat, puis ajouter la crème et le fromage sur le chou-fleur.</t>
         </is>
       </c>
     </row>
@@ -23549,7 +23454,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23912,7 +23817,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Couper les pommes de terre et carottes nouvelles, puis mélanger avec l’huile et les herbes.</t>
+          <t>Couper les pommes de terre et le carottes nouvelles, puis mélanger avec l’huile et les herbes.</t>
         </is>
       </c>
     </row>
@@ -23932,7 +23837,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cuire jusqu’à cuisson complète en surveillant la cuisson de carottes nouvelles.</t>
+          <t>Cuire jusqu’à cuisson complète en surveillant le carottes nouvelles.</t>
         </is>
       </c>
     </row>
@@ -23966,7 +23871,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24329,7 +24234,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Couper les pommes de terre et courgettes, puis mélanger avec l’huile et les herbes.</t>
+          <t>Couper les pommes de terre et le courgettes, puis mélanger avec l’huile et les herbes.</t>
         </is>
       </c>
     </row>
@@ -24349,7 +24254,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cuire jusqu’à cuisson complète en surveillant la cuisson de courgettes.</t>
+          <t>Cuire jusqu’à cuisson complète en surveillant le courgettes.</t>
         </is>
       </c>
     </row>
@@ -24383,7 +24288,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24746,7 +24651,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Couper les pommes de terre et panais, puis mélanger avec l’huile et les herbes.</t>
+          <t>Couper les pommes de terre et le panais, puis mélanger avec l’huile et les herbes.</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24671,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cuire jusqu’à cuisson complète en surveillant la cuisson de panais.</t>
+          <t>Cuire jusqu’à cuisson complète en surveillant le panais.</t>
         </is>
       </c>
     </row>
@@ -24800,7 +24705,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25163,7 +25068,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Couper les pommes de terre et carottes, puis mélanger avec l’huile et les herbes.</t>
+          <t>Couper les pommes de terre et le carottes, puis mélanger avec l’huile et les herbes.</t>
         </is>
       </c>
     </row>
@@ -25183,7 +25088,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cuire jusqu’à cuisson complète en surveillant la cuisson de carottes.</t>
+          <t>Cuire jusqu’à cuisson complète en surveillant le carottes.</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25122,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25750,7 +25655,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26133,7 +26038,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cuire le riz et préparer haricots verts.</t>
+          <t>Cuire le riz et préparer les haricots verts.</t>
         </is>
       </c>
     </row>
@@ -26153,7 +26058,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ajouter haricots verts, puis la moutarde et la crème.</t>
+          <t>Ajouter les haricots verts, puis la moutarde et la crème.</t>
         </is>
       </c>
     </row>
@@ -26197,7 +26102,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26610,7 +26515,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27023,7 +26928,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27496,7 +27401,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27939,7 +27844,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -28382,7 +28287,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -28945,7 +28850,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -29418,7 +29323,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -29771,7 +29676,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30274,7 +30179,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30657,7 +30562,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31040,7 +30945,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cuire le riz et préparer brocoli.</t>
+          <t>Cuire le riz et préparer les brocoli.</t>
         </is>
       </c>
     </row>
@@ -31060,7 +30965,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ajouter brocoli, puis la moutarde et la crème.</t>
+          <t>Ajouter les brocoli, puis la moutarde et la crème.</t>
         </is>
       </c>
     </row>
@@ -31104,7 +31009,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31577,7 +31482,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32050,7 +31955,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32463,7 +32368,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32876,7 +32781,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -33349,7 +33254,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -33852,7 +33757,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -34265,7 +34170,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -34704,7 +34609,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
     </row>
@@ -35050,7 +34955,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
     </row>
@@ -35370,7 +35275,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -35753,7 +35658,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cuire le riz et préparer carottes.</t>
+          <t>Cuire le riz et préparer les carottes.</t>
         </is>
       </c>
     </row>
@@ -35773,7 +35678,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ajouter carottes, puis la moutarde et la crème.</t>
+          <t>Ajouter les carottes, puis la moutarde et la crème.</t>
         </is>
       </c>
     </row>
@@ -35813,7 +35718,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
     </row>
@@ -36189,7 +36094,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
     </row>
@@ -36565,7 +36470,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
     </row>
@@ -36851,7 +36756,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
     </row>
@@ -37077,7 +36982,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
     </row>
@@ -37337,7 +37242,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -37770,7 +37675,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ajouter asperges et les pois chiches, puis verser le lait de coco.</t>
+          <t>Ajouter le asperges et les pois chiches, puis verser le lait de coco.</t>
         </is>
       </c>
     </row>
@@ -37814,7 +37719,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -38247,7 +38152,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ajouter poivrons et les pois chiches, puis verser le lait de coco.</t>
+          <t>Ajouter le poivrons et les pois chiches, puis verser le lait de coco.</t>
         </is>
       </c>
     </row>
@@ -38291,7 +38196,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.11.0</t>
+          <t>4.12.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -38724,7 +38629,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ajouter courge et les pois chiches, puis verser le lait de coco.</t>
+          <t>Ajouter le courge et les pois chiches, puis verser le lait de coco.</t>
         </is>
       </c>
     </row>

--- a/recettes.xlsx
+++ b/recettes.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
     </row>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -10865,7 +10865,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -11312,7 +11312,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13457,7 +13457,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -14260,7 +14260,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -17082,7 +17082,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18243,7 +18243,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18630,7 +18630,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21042,7 +21042,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22293,7 +22293,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22680,7 +22680,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23067,7 +23067,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23871,7 +23871,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24288,7 +24288,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24705,7 +24705,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25655,7 +25655,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26515,7 +26515,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26928,7 +26928,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27401,7 +27401,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27844,7 +27844,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -28287,7 +28287,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -28850,7 +28850,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -29323,7 +29323,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -29676,7 +29676,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30179,7 +30179,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30562,7 +30562,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31009,7 +31009,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31482,7 +31482,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32368,7 +32368,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -33757,7 +33757,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -34170,7 +34170,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -34609,7 +34609,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
     </row>
@@ -34955,7 +34955,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
     </row>
@@ -35275,7 +35275,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -35718,7 +35718,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
     </row>
@@ -36094,7 +36094,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
     </row>
@@ -36470,7 +36470,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
     </row>
@@ -36756,7 +36756,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
     </row>
@@ -36982,7 +36982,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
     </row>
@@ -37242,7 +37242,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -37719,7 +37719,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -38196,7 +38196,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.12.0</t>
+          <t>4.13.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>

--- a/recettes.xlsx
+++ b/recettes.xlsx
@@ -70,6 +70,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dessert Riz au lait" sheetId="62" state="visible" r:id="rId62"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dessert Mousse au chocolat" sheetId="63" state="visible" r:id="rId63"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dessert Compote pomme-cannelle" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarte tatin de tomates, burrata" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tian de légumes, œufs et quinoa" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Courge farcie au gorgonzola et " sheetId="67" state="visible" r:id="rId67"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salade d’endives, feta et noix" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soupe poireaux, carottes et nav" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soupe oignons, pommes de terre " sheetId="70" state="visible" r:id="rId70"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purée de pommes de terre et sau" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riz sauté aux œufs et légumes" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poulet paprika, boulgour et car" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omelette au fromage, pommes de " sheetId="74" state="visible" r:id="rId74"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poivrons farcis au bœuf et chai" sheetId="75" state="visible" r:id="rId75"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -574,7 +585,7 @@
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1342,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Fenouil)</t>
+          <t>Colin et riz, de saison (Fenouil)</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3134,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Tomates)</t>
+          <t>Colin et riz, de saison (Tomates)</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4926,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Chou-fleur)</t>
+          <t>Colin et riz, de saison (Chou-fleur)</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5694,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Chou-fleur)</t>
+          <t>Colin et riz, de saison (Chou-fleur)</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6718,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Endives)</t>
+          <t>Colin et riz, de saison (Endives)</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7486,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Endives)</t>
+          <t>Colin et riz, de saison (Endives)</t>
         </is>
       </c>
     </row>
@@ -9941,7 +9952,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -10418,7 +10429,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -10865,7 +10876,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -11312,7 +11323,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -11759,7 +11770,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12206,7 +12217,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -12623,7 +12634,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13040,7 +13051,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13457,7 +13468,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13874,7 +13885,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -13890,7 +13901,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Fenouil)</t>
+          <t>Colin et riz, de saison (Fenouil)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -13906,7 +13917,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz Fenouil</t>
+          <t>Colin et riz Fenouil</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -13938,7 +13949,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz</t>
+          <t>Colin et riz</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -14055,7 +14066,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cabillaud</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -14217,7 +14228,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Déposer le cabillaud, couvrir et cuire doucement.</t>
+          <t>Déposer le colin, couvrir et cuire doucement.</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14250,6 +14261,8 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14260,7 +14273,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -14295,6 +14308,16 @@
           <t>Rôle</t>
         </is>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Équivalence quantité</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Équivalence unité</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14503,7 +14526,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -14524,11 +14547,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cabillaud</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -14570,6 +14593,14 @@
           <t>Fond de placard</t>
         </is>
       </c>
+      <c r="F13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14628,7 +14659,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -14698,7 +14729,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -14915,15 +14946,23 @@
           <t>Fond de placard</t>
         </is>
       </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Escalope de poulet</t>
+          <t>Farine</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -14932,23 +14971,23 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Boucherie</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Féculent</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Farine</t>
+          <t>Fraise</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -14957,23 +14996,23 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Féculent</t>
+          <t>Fruit</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fraise</t>
+          <t>Fromage</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>17.2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -14982,57 +15021,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Crèmerie</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fromage</t>
+          <t>Galette de sarrasin</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.2</v>
+        <v>1.2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Crèmerie</t>
+          <t>Boulangerie</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Féculent</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Galette de sarrasin</t>
+          <t>Gnocchi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Boulangerie</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -15044,11 +15083,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gnocchi</t>
+          <t>Gorgonzola</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -15057,23 +15096,23 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Crèmerie</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Féculent</t>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gorgonzola</t>
+          <t>Haricots rouges</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -15082,23 +15121,23 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Crèmerie</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Complément</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Haricots rouges</t>
+          <t>Haricots verts</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -15107,23 +15146,23 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Légume</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Haricots verts</t>
+          <t>Herbes de Provence</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -15132,27 +15171,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>g</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Herbes de Provence</t>
+          <t>Huile d’olive</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -15169,32 +15216,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Huile d’olive</t>
+          <t>Jambon</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Boucherie</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fond de placard</t>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jambon</t>
+          <t>Jus de citron</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -15202,24 +15249,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>c. à soupe</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Boucherie</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Complément</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jus de citron</t>
+          <t>Kiwi</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -15227,53 +15274,53 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>c. à soupe</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Fruit</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kiwi</t>
+          <t>Lait</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Crèmerie</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Complément</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lait</t>
+          <t>Lait de coco</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -15282,7 +15329,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Crèmerie</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -15294,32 +15341,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lait de coco</t>
+          <t>Lardons</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Boucherie</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Lardons</t>
+          <t>Lasagnes</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -15332,23 +15379,23 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Boucherie</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Féculent</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lasagnes</t>
+          <t>Lentilles corail</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -15362,18 +15409,18 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Féculent</t>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lentilles corail</t>
+          <t>Lentilles vertes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -15394,11 +15441,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Lentilles vertes</t>
+          <t>Levure chimique</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -15412,39 +15459,39 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Fond de placard</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Levure chimique</t>
+          <t>Mandarine</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fond de placard</t>
+          <t>Fruit</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mandarine</t>
+          <t>Mayonnaise</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -15452,32 +15499,32 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>c. à café</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Complément</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mayonnaise</t>
+          <t>Maïs</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>c. à café</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -15487,39 +15534,39 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Légume</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Maïs</t>
+          <t>Melon</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Fruit</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Melon</t>
+          <t>Moutarde</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -15527,24 +15574,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>c. à soupe</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Complément</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Moutarde</t>
+          <t>Naan fromage</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -15552,24 +15599,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>c. à soupe</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Boulangerie</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Féculent</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Naan fromage</t>
+          <t>Nectarine</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -15582,57 +15629,57 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Boulangerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Féculent</t>
+          <t>Fruit</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Nectarine</t>
+          <t>Noix</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Complément</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Noix</t>
+          <t>Oignon</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -15644,7 +15691,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Oignon</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -15662,47 +15709,47 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Fruit</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Boulangerie</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Féculent</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Pain burger</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -15719,15 +15766,15 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pain burger</t>
+          <t>Pain complet</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -15744,15 +15791,15 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pain complet</t>
+          <t>Pain de mie</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -15769,7 +15816,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pain de mie</t>
+          <t>Pamplemousse</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -15782,48 +15829,48 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Boulangerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Féculent</t>
+          <t>Fruit</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pamplemousse</t>
+          <t>Parmesan</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Crèmerie</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Parmesan</t>
+          <t>Petits pois</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>28</v>
+        <v>4.5</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -15832,27 +15879,27 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Crèmerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Légume</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Petits pois</t>
+          <t>Poire</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -15862,22 +15909,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Fruit</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Poire</t>
+          <t>Poireaux</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -15887,18 +15934,18 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Légume</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Poireaux</t>
+          <t>Pois chiches</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -15907,52 +15954,52 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Pois chiches</t>
+          <t>Poivron</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Légume</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Poivron</t>
+          <t>Poivrons</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -15969,56 +16016,56 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Poivrons</t>
+          <t>Pomme</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4.2</v>
+        <v>0.48</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>Fruits &amp; légumes</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Légume</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Pomme</t>
+          <t>Pommes de terre</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.48</v>
+        <v>2</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Complément</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Pommes de terre</t>
+          <t>Potiron</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -16032,18 +16079,18 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Légume</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Potiron</t>
+          <t>Escalope de poulet</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2.8</v>
+        <v>14</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -16052,23 +16099,23 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Boucherie</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Poulet</t>
+          <t>Poulet entier</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -16089,32 +16136,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Poulet rôti</t>
+          <t>Prune</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Boucherie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Fruit</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Prune</t>
+          <t>Pâte brisée</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -16127,27 +16174,27 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Féculent</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Pâte brisée</t>
+          <t>Pâtes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -16164,61 +16211,61 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Pâtes</t>
+          <t>Pêche</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Féculent</t>
+          <t>Fruit</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Pêche</t>
+          <t>Quinoa</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Féculent</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Quinoa</t>
+          <t>Riz</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -16239,7 +16286,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Riz</t>
+          <t>Riz rond</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -16255,20 +16302,15 @@
           <t>Épicerie</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Féculent</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Riz rond</t>
+          <t>Riz à risotto</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -16278,42 +16320,47 @@
       <c r="D82" t="inlineStr">
         <is>
           <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Féculent</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Riz à risotto</t>
+          <t>Salade romaine</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Féculent</t>
+          <t>Légume</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Salade romaine</t>
+          <t>Salade verte</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -16334,32 +16381,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Salade verte</t>
+          <t>Sardines</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>boîte</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Poissonnerie</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sardines</t>
+          <t>Saucisse de Morteau</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -16367,12 +16414,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>boîte</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Poissonnerie</t>
+          <t>Boucherie</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -16384,20 +16431,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Saucisse de Morteau</t>
+          <t>Saumon</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Boucherie</t>
+          <t>Poissonnerie</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -16409,11 +16456,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Saumon</t>
+          <t>Semoule</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>25</v>
+        <v>2.8</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -16422,57 +16469,57 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Poissonnerie</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Féculent</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Semoule</t>
+          <t>Steak haché</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Boucherie</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Féculent</t>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Steak haché</t>
+          <t>Stracciatella</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Boucherie</t>
+          <t>Crèmerie</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -16484,11 +16531,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Stracciatella</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -16497,23 +16544,23 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Crèmerie</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Complément</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Thon</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -16522,19 +16569,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Poissonnerie</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Thon</t>
+          <t>Tomates</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -16547,23 +16594,23 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Poissonnerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Légume</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tomates</t>
+          <t>Tomates concassées</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -16572,7 +16619,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -16584,15 +16631,15 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tomates concassées</t>
+          <t>Vanille</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -16602,43 +16649,46 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>5</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ml</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Vanille</t>
+          <t>Yaourt</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>55</v>
+        <v>0.55</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Épicerie</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Fond de placard</t>
+          <t>Crèmerie</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Yaourt</t>
+          <t>Échalotes</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -16647,14 +16697,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Crèmerie</t>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Légume</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Échalotes</t>
+          <t>Épices guacamole</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -16662,103 +16717,103 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>sachet</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Épicerie</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Complément</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Épices guacamole</t>
+          <t>Épinards</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>sachet</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Épicerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Légume</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Épinards</t>
+          <t>Œufs</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5</v>
+        <v>0.35</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>unité</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Fruits &amp; légumes</t>
+          <t>Crèmerie</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Légume</t>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Œufs</t>
+          <t>Asperges</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.35</v>
+        <v>16</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>unité</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Crèmerie</t>
+          <t>Fruits &amp; légumes</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Protéine</t>
+          <t>Légume</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Asperges</t>
+          <t>Artichaut</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>16</v>
+        <v>7.5</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -16779,11 +16834,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Artichaut</t>
+          <t>Fenouil</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -16804,11 +16859,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Fenouil</t>
+          <t>Fèves</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -16829,11 +16884,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Fèves</t>
+          <t>Blettes</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -16854,11 +16909,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Blettes</t>
+          <t>Betterave</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -16879,11 +16934,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Betterave</t>
+          <t>Brocoli</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -16904,11 +16959,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Brocoli</t>
+          <t>Champignons</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -16929,11 +16984,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Champignons</t>
+          <t>Chou-fleur</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -16954,7 +17009,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Chou-fleur</t>
+          <t>Panais</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -16979,11 +17034,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Panais</t>
+          <t>Endives</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -17004,11 +17059,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Endives</t>
+          <t>Chou vert</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -17029,25 +17084,233 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Chou vert</t>
+          <t>Burrata</t>
         </is>
       </c>
       <c r="B113" t="n">
+        <v>20</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Feta</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>16</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Pâte feuilletée</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Boulgour</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Navet</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
         <v>3.2</v>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>Fruits &amp; légumes</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>Légume</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Riz complet</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Chair à saucisse</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>12</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Boucherie</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Paprika</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>28</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>2</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Saucisse</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Boucherie</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Protéine</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17345,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17098,7 +17361,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Tomates)</t>
+          <t>Colin et riz, de saison (Tomates)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -17114,7 +17377,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz Tomates</t>
+          <t>Colin et riz Tomates</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -17146,7 +17409,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz</t>
+          <t>Colin et riz</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -17263,7 +17526,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cabillaud</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -17425,7 +17688,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Déposer le cabillaud, couvrir et cuire doucement.</t>
+          <t>Déposer le colin, couvrir et cuire doucement.</t>
         </is>
       </c>
     </row>
@@ -17469,7 +17732,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17485,7 +17748,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Chou-fleur)</t>
+          <t>Colin et riz, de saison (Chou-fleur)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -17501,7 +17764,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz Chou-fleur</t>
+          <t>Colin et riz Chou-fleur</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -17533,7 +17796,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz</t>
+          <t>Colin et riz</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -17650,7 +17913,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cabillaud</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -17812,7 +18075,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Déposer le cabillaud, couvrir et cuire doucement.</t>
+          <t>Déposer le colin, couvrir et cuire doucement.</t>
         </is>
       </c>
     </row>
@@ -17856,7 +18119,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -17872,7 +18135,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz, de saison (Endives)</t>
+          <t>Colin et riz, de saison (Endives)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -17888,7 +18151,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz Endives</t>
+          <t>Colin et riz Endives</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -17920,7 +18183,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Cabillaud et riz</t>
+          <t>Colin et riz</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -18037,7 +18300,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cabillaud</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -18199,7 +18462,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Déposer le cabillaud, couvrir et cuire doucement.</t>
+          <t>Déposer le colin, couvrir et cuire doucement.</t>
         </is>
       </c>
     </row>
@@ -18243,7 +18506,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -18630,7 +18893,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19017,7 +19280,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19404,7 +19667,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -19791,7 +20054,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20208,7 +20471,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -20625,7 +20888,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21042,7 +21305,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21223,7 +21486,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Poulet</t>
+          <t>Escalope de poulet</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -21489,7 +21752,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -21906,7 +22169,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22135,7 +22398,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Féculent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -22293,7 +22556,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22522,7 +22785,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Féculent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -22680,7 +22943,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -22909,7 +23172,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Féculent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -23067,7 +23330,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23296,7 +23559,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Féculent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -23454,7 +23717,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -23635,7 +23898,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Poulet rôti</t>
+          <t>Poulet entier</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -23683,7 +23946,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Féculent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -23871,7 +24134,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24052,7 +24315,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Poulet rôti</t>
+          <t>Poulet entier</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -24100,7 +24363,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Féculent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -24288,7 +24551,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24469,7 +24732,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Poulet rôti</t>
+          <t>Poulet entier</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -24517,7 +24780,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Féculent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -24705,7 +24968,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -24886,7 +25149,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Poulet rôti</t>
+          <t>Poulet entier</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -24934,7 +25197,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Féculent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -25122,7 +25385,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25655,7 +25918,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -25836,7 +26099,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Poulet</t>
+          <t>Escalope de poulet</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -26102,7 +26365,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26357,7 +26620,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Féculent</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -26515,7 +26778,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -26928,7 +27191,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27401,7 +27664,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -27626,7 +27889,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Féculent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -27844,7 +28107,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -28287,7 +28550,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -28363,7 +28626,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Végétarien</t>
+          <t>Viande</t>
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -28850,7 +29113,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -29323,7 +29586,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -29676,7 +29939,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30179,7 +30442,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30562,7 +30825,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -30743,7 +31006,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Poulet</t>
+          <t>Escalope de poulet</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -31009,7 +31272,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31482,7 +31745,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -31737,7 +32000,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Complément</t>
+          <t>Féculent</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -31955,7 +32218,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32368,7 +32631,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -32781,7 +33044,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -33254,7 +33517,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -33757,7 +34020,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -34170,7 +34433,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -34609,7 +34872,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
     </row>
@@ -34955,7 +35218,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
     </row>
@@ -35275,7 +35538,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -35456,7 +35719,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Poulet</t>
+          <t>Escalope de poulet</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -35718,7 +35981,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
     </row>
@@ -36094,7 +36357,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
     </row>
@@ -36470,7 +36733,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
     </row>
@@ -36756,7 +37019,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
     </row>
@@ -36982,7 +37245,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
     </row>
@@ -37209,6 +37472,2471 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>Écraser ou mixer, puis laisser refroidir.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FICHE RECETTE</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>4.14.0</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Tarte tatin de tomates, burrata et salade</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nom compact</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Tarte tatin de tomates, burrata et salade</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Type structurel</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Recette saisonnière</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Fromage</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Temps (min)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Coût</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Calculé par l’application</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>INGRÉDIENTS PAR PERSONNE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Groupe nutritionnel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tomates</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>250</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Burrata</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>75</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pâte feuilletée</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Salade verte</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Moutarde</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>c. à café</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Huile d’olive</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Herbes de Provence</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>c. à café</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ÉTAPES DE PRÉPARATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Préchauffer le four à 190 °C et disposer les tomates dans le moule avec les herbes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cuire les tomates 15 minutes, puis couvrir avec la pâte feuilletée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Poursuivre la cuisson environ 25 minutes et retourner la tarte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ajouter la burrata et servir avec la salade.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FICHE RECETTE</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>4.14.0</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Tian de légumes, œufs et quinoa</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nom compact</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Tian de légumes, œufs et quinoa</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Type structurel</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Recette saisonnière</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Végétarien</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Temps (min)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Coût</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Calculé par l’application</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>INGRÉDIENTS PAR PERSONNE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Groupe nutritionnel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Courgettes</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Aubergine</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tomates</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Quinoa</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>60</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Œufs</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ail</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>gousse</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Huile d’olive</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Herbes de Provence</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>c. à café</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ÉTAPES DE PRÉPARATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Préchauffer le four à 190 °C et couper les légumes en rondelles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ranger les légumes dans un plat avec l’ail, l’huile et les herbes, puis cuire 35 minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cuire le quinoa et les œufs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Servir le tian avec le quinoa et les œufs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FICHE RECETTE</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>4.14.0</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Courge farcie au gorgonzola et noix</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nom compact</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Courge farcie au gorgonzola et noix</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Type structurel</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Recette saisonnière</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Fromage</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Temps (min)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Autumn,Winter</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Coût</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Calculé par l’application</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>INGRÉDIENTS PAR PERSONNE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Groupe nutritionnel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Courge</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>300</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Boulgour</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>60</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gorgonzola</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>60</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Noix</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Huile d’olive</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ÉTAPES DE PRÉPARATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Préchauffer le four à 190 °C, couper la courge et retirer les graines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cuire la courge au four et préparer le boulgour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mélanger le boulgour avec l’oignon, le gorgonzola et les noix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Garnir la courge et gratiner 10 minutes.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FICHE RECETTE</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>4.14.0</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Salade d’endives, feta et noix</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nom compact</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Salade d’endives, feta et noix</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Type structurel</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Recette saisonnière</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Fromage</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Temps (min)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Autumn,Winter</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Coût</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Calculé par l’application</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>INGRÉDIENTS PAR PERSONNE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Groupe nutritionnel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Endives</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>180</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Feta</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>60</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Noix</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>20</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pomme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pain complet</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>60</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Boulangerie</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Moutarde</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>c. à café</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Huile d’olive</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ÉTAPES DE PRÉPARATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Émincer les endives et couper la pomme et la feta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mélanger la moutarde et l’huile pour préparer la vinaigrette.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Assembler les endives, la pomme, la feta et les noix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Servir avec le pain complet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FICHE RECETTE</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>4.14.0</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Soupe poireaux, carottes et navets</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nom compact</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Soupe poireaux, carottes et navets</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Type structurel</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Recette saisonnière</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Fromage</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Temps (min)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Autumn,Winter</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Coût</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Calculé par l’application</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>INGRÉDIENTS PAR PERSONNE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Groupe nutritionnel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Poireaux</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Navet</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pommes de terre</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chèvre</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>60</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Pain complet</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>60</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Boulangerie</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bouillon de légumes</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cube</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Huile d’olive</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ÉTAPES DE PRÉPARATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nettoyer et couper les légumes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Faire revenir l’oignon, puis ajouter les légumes et le bouillon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cuire environ 30 minutes et mixer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Faire griller le pain avec le chèvre et servir avec la soupe.</t>
         </is>
       </c>
     </row>
@@ -37242,7 +39970,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -37686,6 +40414,2742 @@
       <c r="B24" t="inlineStr">
         <is>
           <t>Mijoter 15 à 20 minutes et servir avec le riz.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FICHE RECETTE</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>4.14.0</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Soupe oignons, pommes de terre et ail</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nom compact</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Soupe oignons, pommes de terre et ail</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Type structurel</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Recette saisonnière</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Fromage</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Temps (min)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Winter</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Coût</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Calculé par l’application</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>INGRÉDIENTS PAR PERSONNE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Groupe nutritionnel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Pommes de terre</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>180</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ail</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>gousse</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bouillon de légumes</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>cube</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>60</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Boulangerie</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Comté</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>50</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Huile d’olive</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ÉTAPES DE PRÉPARATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Émincer les oignons et couper les pommes de terre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Faire revenir les oignons et l’ail, puis ajouter les pommes de terre et le bouillon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cuire environ 30 minutes et mixer partiellement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Gratiner le pain avec le comté et servir avec la soupe.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FICHE RECETTE</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>4.14.0</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Purée de pommes de terre et saucisse</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nom compact</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Purée de pommes de terre et saucisse</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Type structurel</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Recette saisonnière</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Viande</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Temps (min)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Winter</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Coût</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Calculé par l’application</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>INGRÉDIENTS PAR PERSONNE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Groupe nutritionnel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Pommes de terre</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>250</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lait</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>75</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Beurre</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saucisse</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Boucherie</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>180</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Moutarde</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>c. à café</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ÉTAPES DE PRÉPARATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cuire les pommes de terre et les carottes séparément.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Écraser les pommes de terre avec le lait et le beurre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cuire la saucisse jusqu’à cuisson complète.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Servir la purée avec la saucisse, les carottes et la moutarde.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FICHE RECETTE</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>4.14.0</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Riz sauté aux œufs et légumes</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nom compact</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Riz sauté aux œufs et légumes</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Type structurel</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Recette intemporelle</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Végétarien</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Temps (min)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Spring,Summer,Autumn,Winter</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Coût</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Calculé par l’application</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>INGRÉDIENTS PAR PERSONNE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Groupe nutritionnel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Riz</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>60</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Œufs</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Petits pois</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Huile d’olive</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ÉTAPES DE PRÉPARATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cuire le riz et le laisser tiédir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Faire revenir l’oignon, les carottes et les petits pois.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ajouter les œufs battus et mélanger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Incorporer le riz et faire sauter quelques minutes.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FICHE RECETTE</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>4.14.0</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Poulet paprika, boulgour et carottes</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nom compact</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Poulet paprika, boulgour et carottes</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Type structurel</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Recette intemporelle</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Viande</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Temps (min)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Spring,Summer,Autumn,Winter</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Coût</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Calculé par l’application</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>INGRÉDIENTS PAR PERSONNE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Groupe nutritionnel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Escalope de poulet</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>150</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Boucherie</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Boulgour</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>60</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Carottes</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>180</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Paprika</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>c. à café</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Huile d’olive</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ÉTAPES DE PRÉPARATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cuire le boulgour et couper les carottes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Faire revenir l’oignon et les carottes avec l’huile et le paprika.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ajouter le poulet et cuire complètement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Servir avec le boulgour.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FICHE RECETTE</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>4.14.0</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Omelette au fromage, pommes de terre et salade</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nom compact</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Omelette au fromage, pommes de terre et salade</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Type structurel</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Recette intemporelle</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Fromage</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Temps (min)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Spring,Summer,Autumn,Winter</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Coût</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Calculé par l’application</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>INGRÉDIENTS PAR PERSONNE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Groupe nutritionnel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Œufs</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fromage</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>40</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Crèmerie</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pommes de terre</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>200</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Salade verte</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Huile d’olive</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ÉTAPES DE PRÉPARATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cuire les pommes de terre en dés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Battre les œufs et ajouter le fromage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cuire l’omelette avec les pommes de terre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Servir avec la salade.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>FICHE RECETTE</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>4.14.0</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Poivrons farcis au bœuf et chair à saucisse, riz complet</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nom compact</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Poivrons farcis au bœuf et chair à saucisse, riz complet</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Type structurel</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Recette intemporelle</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Viande</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Temps (min)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Spring,Summer,Autumn,Winter</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Coût</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Calculé par l’application</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>INGRÉDIENTS PAR PERSONNE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ingrédient</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Groupe nutritionnel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Poivrons</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>250</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bœuf haché</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>75</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Boucherie</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chair à saucisse</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>75</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Boucherie</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Protéine</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Riz complet</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>60</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Féculent</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Oignon</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fruits &amp; légumes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Complément</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tomates concassées</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Légume</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Herbes de Provence</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>c. à café</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Épicerie</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fond de placard</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Toutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ÉTAPES DE PRÉPARATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Étape</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Préchauffer le four à 190 °C et préparer les poivrons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Faire revenir l’oignon, le bœuf et la chair à saucisse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ajouter les tomates et les herbes, puis farcir les poivrons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cuire 35 minutes et servir avec le riz complet.</t>
         </is>
       </c>
     </row>
@@ -37719,7 +43183,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
@@ -38196,7 +43660,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>4.13.0</t>
+          <t>4.14.0</t>
         </is>
       </c>
       <c r="C1" s="4" t="n"/>
